--- a/crop_area_by_provinces_TEMPLATE.xlsx
+++ b/crop_area_by_provinces_TEMPLATE.xlsx
@@ -5,15 +5,15 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/pongthanatburanachon/Downloads/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/pongthanatburanachon/Desktop/work/dashboard/crop_timeline/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6928AFC3-B493-0049-9BD8-800130F10360}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D642E483-59AB-A446-8B09-0AFDF84F92D7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="40120" yWindow="-4220" windowWidth="30240" windowHeight="18880" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="38400" yWindow="-4400" windowWidth="30240" windowHeight="18880" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="crop_area_by_province" sheetId="1" r:id="rId1"/>
+    <sheet name="crop_area_by_provinces" sheetId="1" r:id="rId1"/>
     <sheet name="province_lookup" sheetId="2" r:id="rId2"/>
   </sheets>
   <calcPr calcId="0"/>
@@ -21,7 +21,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="193" uniqueCount="99">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="199" uniqueCount="102">
   <si>
     <t>province_name_en</t>
   </si>
@@ -318,6 +318,15 @@
   </si>
   <si>
     <t>SHK_region</t>
+  </si>
+  <si>
+    <t>R1</t>
+  </si>
+  <si>
+    <t>R2</t>
+  </si>
+  <si>
+    <t>R3</t>
   </si>
 </sst>
 </file>
@@ -766,6 +775,9 @@
       <c r="G2" s="7">
         <v>508845</v>
       </c>
+      <c r="H2" t="s">
+        <v>99</v>
+      </c>
       <c r="I2" s="4"/>
     </row>
     <row r="3" spans="1:9" x14ac:dyDescent="0.2">
@@ -790,6 +802,9 @@
       <c r="G3" s="7">
         <v>95378</v>
       </c>
+      <c r="H3" t="s">
+        <v>100</v>
+      </c>
       <c r="I3" s="4"/>
     </row>
     <row r="4" spans="1:9" x14ac:dyDescent="0.2">
@@ -814,6 +829,9 @@
       <c r="G4" s="7">
         <v>58624</v>
       </c>
+      <c r="H4" t="s">
+        <v>101</v>
+      </c>
       <c r="I4" s="4"/>
     </row>
     <row r="5" spans="1:9" x14ac:dyDescent="0.2">
@@ -838,6 +856,9 @@
       <c r="G5" s="8">
         <v>1109790</v>
       </c>
+      <c r="H5" t="s">
+        <v>99</v>
+      </c>
     </row>
     <row r="6" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A6" s="3" t="s">
@@ -861,6 +882,9 @@
       <c r="G6" s="8">
         <v>559308</v>
       </c>
+      <c r="H6" t="s">
+        <v>100</v>
+      </c>
     </row>
     <row r="7" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A7" s="3" t="s">
@@ -883,6 +907,9 @@
       </c>
       <c r="G7" s="8">
         <v>425641</v>
+      </c>
+      <c r="H7" t="s">
+        <v>101</v>
       </c>
     </row>
     <row r="8" spans="1:9" x14ac:dyDescent="0.2">

--- a/crop_area_by_provinces_TEMPLATE.xlsx
+++ b/crop_area_by_provinces_TEMPLATE.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/pongthanatburanachon/Desktop/work/dashboard/crop_timeline/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D642E483-59AB-A446-8B09-0AFDF84F92D7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2F0AE34A-AFCA-7542-BF6D-810497CEE94D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="38400" yWindow="-4400" windowWidth="30240" windowHeight="18880" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -21,7 +21,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="199" uniqueCount="102">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="203" uniqueCount="106">
   <si>
     <t>province_name_en</t>
   </si>
@@ -327,6 +327,18 @@
   </si>
   <si>
     <t>R3</t>
+  </si>
+  <si>
+    <t>fertilizer_usage</t>
+  </si>
+  <si>
+    <t>herbicide_usage</t>
+  </si>
+  <si>
+    <t>insecticide_usage</t>
+  </si>
+  <si>
+    <t>fungicide_usage</t>
   </si>
 </sst>
 </file>
@@ -712,7 +724,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:I19"/>
+  <dimension ref="A1:L19"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="20" customWidth="1"/>
@@ -723,10 +735,13 @@
     <col min="6" max="6" width="16" customWidth="1"/>
     <col min="7" max="7" width="18" customWidth="1"/>
     <col min="8" max="8" width="13.33203125" customWidth="1"/>
-    <col min="9" max="9" width="55" customWidth="1"/>
+    <col min="9" max="9" width="15.6640625" customWidth="1"/>
+    <col min="10" max="10" width="15.6640625" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="17.1640625" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="15.83203125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -751,9 +766,20 @@
       <c r="H1" s="1" t="s">
         <v>98</v>
       </c>
-      <c r="I1" s="2"/>
-    </row>
-    <row r="2" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="I1" s="2" t="s">
+        <v>102</v>
+      </c>
+      <c r="J1" s="1" t="s">
+        <v>103</v>
+      </c>
+      <c r="K1" s="1" t="s">
+        <v>104</v>
+      </c>
+      <c r="L1" s="1" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="2" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A2" s="3" t="s">
         <v>29</v>
       </c>
@@ -780,7 +806,7 @@
       </c>
       <c r="I2" s="4"/>
     </row>
-    <row r="3" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A3" s="3" t="s">
         <v>60</v>
       </c>
@@ -807,7 +833,7 @@
       </c>
       <c r="I3" s="4"/>
     </row>
-    <row r="4" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A4" s="3" t="s">
         <v>39</v>
       </c>
@@ -834,7 +860,7 @@
       </c>
       <c r="I4" s="4"/>
     </row>
-    <row r="5" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A5" s="3" t="s">
         <v>29</v>
       </c>
@@ -860,7 +886,7 @@
         <v>99</v>
       </c>
     </row>
-    <row r="6" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A6" s="3" t="s">
         <v>60</v>
       </c>
@@ -886,7 +912,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="7" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A7" s="3" t="s">
         <v>39</v>
       </c>
@@ -912,31 +938,31 @@
         <v>101</v>
       </c>
     </row>
-    <row r="8" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A8" s="3"/>
     </row>
-    <row r="9" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A9" s="3"/>
     </row>
-    <row r="10" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A10" s="3"/>
     </row>
-    <row r="11" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A11" s="3"/>
     </row>
-    <row r="12" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A12" s="3"/>
     </row>
-    <row r="13" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A13" s="3"/>
     </row>
-    <row r="14" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A14" s="3"/>
     </row>
-    <row r="15" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A15" s="3"/>
     </row>
-    <row r="16" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A16" s="3"/>
     </row>
     <row r="17" spans="1:1" x14ac:dyDescent="0.2">

--- a/crop_area_by_provinces_TEMPLATE.xlsx
+++ b/crop_area_by_provinces_TEMPLATE.xlsx
@@ -8,20 +8,32 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/pongthanatburanachon/Desktop/work/dashboard/crop_timeline/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2F0AE34A-AFCA-7542-BF6D-810497CEE94D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BE7E8804-63C1-D045-ACF9-5C87B670DB57}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="38400" yWindow="-4400" windowWidth="30240" windowHeight="18880" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="38400" yWindow="-3760" windowWidth="30240" windowHeight="18880" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="crop_area_by_provinces" sheetId="1" r:id="rId1"/>
     <sheet name="province_lookup" sheetId="2" r:id="rId2"/>
   </sheets>
-  <calcPr calcId="0"/>
+  <calcPr calcId="191029"/>
+  <extLst>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="203" uniqueCount="106">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="212" uniqueCount="114">
   <si>
     <t>province_name_en</t>
   </si>
@@ -339,6 +351,30 @@
   </si>
   <si>
     <t>fungicide_usage</t>
+  </si>
+  <si>
+    <t>Bangkok Metropolis</t>
+  </si>
+  <si>
+    <t>Buri Ram</t>
+  </si>
+  <si>
+    <t>Chon Buri</t>
+  </si>
+  <si>
+    <t>Lop Buri</t>
+  </si>
+  <si>
+    <t>Nong Bua Lam Phu</t>
+  </si>
+  <si>
+    <t>Phangnga</t>
+  </si>
+  <si>
+    <t>Prachin Buri</t>
+  </si>
+  <si>
+    <t>Si Sa Ket</t>
   </si>
 </sst>
 </file>
@@ -378,7 +414,7 @@
       <family val="2"/>
     </font>
   </fonts>
-  <fills count="4">
+  <fills count="6">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -397,6 +433,18 @@
         <bgColor rgb="FFFFF2CC"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1F4E78"/>
+        <bgColor rgb="FF003366"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFF2CC"/>
+        <bgColor rgb="FFFFFFFF"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="1">
     <border>
@@ -410,7 +458,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="9">
+  <cellXfs count="11">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -422,6 +470,8 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="3" fontId="2" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
     <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -999,21 +1049,25 @@
     <col min="1" max="1" width="25" customWidth="1"/>
     <col min="2" max="2" width="12" customWidth="1"/>
     <col min="3" max="4" width="18" customWidth="1"/>
+    <col min="5" max="5" width="21.1640625" customWidth="1"/>
     <col min="6" max="6" width="60" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A1" s="1" t="s">
+      <c r="A1" s="9" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="B1" s="9" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="C1" s="9" t="s">
         <v>14</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="D1" s="9" t="s">
         <v>15</v>
+      </c>
+      <c r="E1" s="9" t="s">
+        <v>98</v>
       </c>
       <c r="F1" s="5" t="s">
         <v>16</v>
@@ -1021,11 +1075,15 @@
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A2" s="6" t="s">
-        <v>17</v>
+        <v>106</v>
       </c>
       <c r="B2" s="6" t="s">
         <v>13</v>
       </c>
+      <c r="C2" s="6" t="s">
+        <v>17</v>
+      </c>
+      <c r="E2" s="10"/>
       <c r="F2" s="5" t="s">
         <v>18</v>
       </c>
@@ -1037,6 +1095,7 @@
       <c r="B3" s="6" t="s">
         <v>11</v>
       </c>
+      <c r="E3" s="10"/>
       <c r="F3" s="5" t="s">
         <v>20</v>
       </c>
@@ -1048,6 +1107,7 @@
       <c r="B4" s="6" t="s">
         <v>13</v>
       </c>
+      <c r="E4" s="10"/>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A5" s="6" t="s">
@@ -1056,14 +1116,19 @@
       <c r="B5" s="6" t="s">
         <v>11</v>
       </c>
+      <c r="E5" s="10"/>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A6" s="6" t="s">
+        <v>107</v>
+      </c>
+      <c r="B6" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="C6" s="6" t="s">
         <v>23</v>
       </c>
-      <c r="B6" s="6" t="s">
-        <v>11</v>
-      </c>
+      <c r="E6" s="10"/>
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A7" s="6" t="s">
@@ -1072,6 +1137,7 @@
       <c r="B7" s="6" t="s">
         <v>25</v>
       </c>
+      <c r="E7" s="10"/>
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A8" s="6" t="s">
@@ -1080,6 +1146,7 @@
       <c r="B8" s="6" t="s">
         <v>13</v>
       </c>
+      <c r="E8" s="10"/>
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A9" s="6" t="s">
@@ -1088,6 +1155,7 @@
       <c r="B9" s="6" t="s">
         <v>11</v>
       </c>
+      <c r="E9" s="10"/>
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A10" s="6" t="s">
@@ -1096,6 +1164,7 @@
       <c r="B10" s="6" t="s">
         <v>25</v>
       </c>
+      <c r="E10" s="10"/>
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A11" s="6" t="s">
@@ -1104,6 +1173,7 @@
       <c r="B11" s="6" t="s">
         <v>8</v>
       </c>
+      <c r="E11" s="10"/>
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A12" s="6" t="s">
@@ -1112,14 +1182,19 @@
       <c r="B12" s="6" t="s">
         <v>8</v>
       </c>
+      <c r="E12" s="10"/>
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A13" s="6" t="s">
-        <v>30</v>
+        <v>108</v>
       </c>
       <c r="B13" s="6" t="s">
         <v>25</v>
       </c>
+      <c r="C13" s="6" t="s">
+        <v>30</v>
+      </c>
+      <c r="E13" s="10"/>
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A14" s="6" t="s">
@@ -1128,6 +1203,7 @@
       <c r="B14" s="6" t="s">
         <v>32</v>
       </c>
+      <c r="E14" s="10"/>
     </row>
     <row r="15" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A15" s="6" t="s">
@@ -1136,6 +1212,7 @@
       <c r="B15" s="6" t="s">
         <v>11</v>
       </c>
+      <c r="E15" s="10"/>
     </row>
     <row r="16" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A16" s="6" t="s">
@@ -1144,502 +1221,580 @@
       <c r="B16" s="6" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="17" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="E16" s="10"/>
+    </row>
+    <row r="17" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A17" s="6" t="s">
         <v>35</v>
       </c>
       <c r="B17" s="6" t="s">
         <v>36</v>
       </c>
-    </row>
-    <row r="18" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="E17" s="10"/>
+    </row>
+    <row r="18" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A18" s="6" t="s">
         <v>37</v>
       </c>
       <c r="B18" s="6" t="s">
         <v>11</v>
       </c>
-    </row>
-    <row r="19" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="E18" s="10"/>
+    </row>
+    <row r="19" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A19" s="6" t="s">
         <v>38</v>
       </c>
       <c r="B19" s="6" t="s">
         <v>32</v>
       </c>
-    </row>
-    <row r="20" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="E19" s="10"/>
+    </row>
+    <row r="20" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A20" s="6" t="s">
         <v>39</v>
       </c>
       <c r="B20" s="6" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="21" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="E20" s="10"/>
+    </row>
+    <row r="21" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A21" s="6" t="s">
         <v>40</v>
       </c>
       <c r="B21" s="6" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="22" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="E21" s="10"/>
+    </row>
+    <row r="22" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A22" s="6" t="s">
         <v>41</v>
       </c>
       <c r="B22" s="6" t="s">
         <v>11</v>
       </c>
-    </row>
-    <row r="23" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="E22" s="10"/>
+    </row>
+    <row r="23" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A23" s="6" t="s">
-        <v>42</v>
+        <v>109</v>
       </c>
       <c r="B23" s="6" t="s">
         <v>13</v>
       </c>
-    </row>
-    <row r="24" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="C23" s="6" t="s">
+        <v>42</v>
+      </c>
+      <c r="E23" s="10"/>
+    </row>
+    <row r="24" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A24" s="6" t="s">
         <v>43</v>
       </c>
       <c r="B24" s="6" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="25" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="E24" s="10"/>
+    </row>
+    <row r="25" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A25" s="6" t="s">
         <v>44</v>
       </c>
       <c r="B25" s="6" t="s">
         <v>11</v>
       </c>
-    </row>
-    <row r="26" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="E25" s="10"/>
+    </row>
+    <row r="26" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A26" s="6" t="s">
         <v>45</v>
       </c>
       <c r="B26" s="6" t="s">
         <v>11</v>
       </c>
-    </row>
-    <row r="27" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="E26" s="10"/>
+    </row>
+    <row r="27" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A27" s="6" t="s">
         <v>46</v>
       </c>
       <c r="B27" s="6" t="s">
         <v>13</v>
       </c>
-    </row>
-    <row r="28" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="E27" s="10"/>
+    </row>
+    <row r="28" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A28" s="6" t="s">
         <v>47</v>
       </c>
       <c r="B28" s="6" t="s">
         <v>13</v>
       </c>
-    </row>
-    <row r="29" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="E28" s="10"/>
+    </row>
+    <row r="29" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A29" s="6" t="s">
         <v>48</v>
       </c>
       <c r="B29" s="6" t="s">
         <v>11</v>
       </c>
-    </row>
-    <row r="30" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="E29" s="10"/>
+    </row>
+    <row r="30" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A30" s="6" t="s">
         <v>10</v>
       </c>
       <c r="B30" s="6" t="s">
         <v>11</v>
       </c>
-    </row>
-    <row r="31" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="E30" s="10"/>
+    </row>
+    <row r="31" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A31" s="6" t="s">
         <v>49</v>
       </c>
       <c r="B31" s="6" t="s">
         <v>13</v>
       </c>
-    </row>
-    <row r="32" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="E31" s="10"/>
+    </row>
+    <row r="32" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A32" s="6" t="s">
         <v>50</v>
       </c>
       <c r="B32" s="6" t="s">
         <v>32</v>
       </c>
-    </row>
-    <row r="33" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="E32" s="10"/>
+    </row>
+    <row r="33" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A33" s="6" t="s">
         <v>51</v>
       </c>
       <c r="B33" s="6" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="34" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="E33" s="10"/>
+    </row>
+    <row r="34" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A34" s="6" t="s">
         <v>52</v>
       </c>
       <c r="B34" s="6" t="s">
         <v>32</v>
       </c>
-    </row>
-    <row r="35" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="E34" s="10"/>
+    </row>
+    <row r="35" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A35" s="6" t="s">
+        <v>110</v>
+      </c>
+      <c r="B35" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="C35" s="6" t="s">
         <v>53</v>
       </c>
-      <c r="B35" s="6" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="36" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="E35" s="10"/>
+    </row>
+    <row r="36" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A36" s="6" t="s">
         <v>54</v>
       </c>
       <c r="B36" s="6" t="s">
         <v>11</v>
       </c>
-    </row>
-    <row r="37" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="E36" s="10"/>
+    </row>
+    <row r="37" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A37" s="6" t="s">
         <v>55</v>
       </c>
       <c r="B37" s="6" t="s">
         <v>13</v>
       </c>
-    </row>
-    <row r="38" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="E37" s="10"/>
+    </row>
+    <row r="38" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A38" s="6" t="s">
         <v>56</v>
       </c>
       <c r="B38" s="6" t="s">
         <v>13</v>
       </c>
-    </row>
-    <row r="39" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="E38" s="10"/>
+    </row>
+    <row r="39" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A39" s="6" t="s">
         <v>57</v>
       </c>
       <c r="B39" s="6" t="s">
         <v>32</v>
       </c>
-    </row>
-    <row r="40" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="E39" s="10"/>
+    </row>
+    <row r="40" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A40" s="6" t="s">
-        <v>58</v>
+        <v>111</v>
       </c>
       <c r="B40" s="6" t="s">
         <v>32</v>
       </c>
-    </row>
-    <row r="41" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="C40" s="6" t="s">
+        <v>58</v>
+      </c>
+      <c r="E40" s="10"/>
+    </row>
+    <row r="41" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A41" s="6" t="s">
         <v>59</v>
       </c>
       <c r="B41" s="6" t="s">
         <v>32</v>
       </c>
-    </row>
-    <row r="42" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="E41" s="10"/>
+    </row>
+    <row r="42" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A42" s="6" t="s">
         <v>60</v>
       </c>
       <c r="B42" s="6" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="43" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="E42" s="10"/>
+    </row>
+    <row r="43" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A43" s="6" t="s">
         <v>61</v>
       </c>
       <c r="B43" s="6" t="s">
         <v>13</v>
       </c>
-    </row>
-    <row r="44" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="E43" s="10"/>
+    </row>
+    <row r="44" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A44" s="6" t="s">
         <v>62</v>
       </c>
       <c r="B44" s="6" t="s">
         <v>36</v>
       </c>
-    </row>
-    <row r="45" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="E44" s="10"/>
+    </row>
+    <row r="45" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A45" s="6" t="s">
         <v>63</v>
       </c>
       <c r="B45" s="6" t="s">
         <v>13</v>
       </c>
-    </row>
-    <row r="46" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="E45" s="10"/>
+    </row>
+    <row r="46" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A46" s="6" t="s">
         <v>64</v>
       </c>
       <c r="B46" s="6" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="47" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="E46" s="10"/>
+    </row>
+    <row r="47" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A47" s="6" t="s">
         <v>65</v>
       </c>
       <c r="B47" s="6" t="s">
         <v>13</v>
       </c>
-    </row>
-    <row r="48" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="E47" s="10"/>
+    </row>
+    <row r="48" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A48" s="6" t="s">
         <v>66</v>
       </c>
       <c r="B48" s="6" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="49" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="E48" s="10"/>
+    </row>
+    <row r="49" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A49" s="6" t="s">
         <v>67</v>
       </c>
       <c r="B49" s="6" t="s">
         <v>32</v>
       </c>
-    </row>
-    <row r="50" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="E49" s="10"/>
+    </row>
+    <row r="50" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A50" s="6" t="s">
-        <v>68</v>
+        <v>112</v>
       </c>
       <c r="B50" s="6" t="s">
         <v>25</v>
       </c>
-    </row>
-    <row r="51" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="C50" s="6" t="s">
+        <v>68</v>
+      </c>
+      <c r="E50" s="10"/>
+    </row>
+    <row r="51" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A51" s="6" t="s">
         <v>69</v>
       </c>
       <c r="B51" s="6" t="s">
         <v>36</v>
       </c>
-    </row>
-    <row r="52" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="E51" s="10"/>
+    </row>
+    <row r="52" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A52" s="6" t="s">
         <v>70</v>
       </c>
       <c r="B52" s="6" t="s">
         <v>32</v>
       </c>
-    </row>
-    <row r="53" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="E52" s="10"/>
+    </row>
+    <row r="53" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A53" s="6" t="s">
         <v>71</v>
       </c>
       <c r="B53" s="6" t="s">
         <v>36</v>
       </c>
-    </row>
-    <row r="54" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="E53" s="10"/>
+    </row>
+    <row r="54" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A54" s="6" t="s">
         <v>72</v>
       </c>
       <c r="B54" s="6" t="s">
         <v>25</v>
       </c>
-    </row>
-    <row r="55" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="E54" s="10"/>
+    </row>
+    <row r="55" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A55" s="6" t="s">
         <v>73</v>
       </c>
       <c r="B55" s="6" t="s">
         <v>11</v>
       </c>
-    </row>
-    <row r="56" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="E55" s="10"/>
+    </row>
+    <row r="56" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A56" s="6" t="s">
         <v>74</v>
       </c>
       <c r="B56" s="6" t="s">
         <v>25</v>
       </c>
-    </row>
-    <row r="57" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="E56" s="10"/>
+    </row>
+    <row r="57" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A57" s="6" t="s">
         <v>75</v>
       </c>
       <c r="B57" s="6" t="s">
         <v>11</v>
       </c>
-    </row>
-    <row r="58" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="E57" s="10"/>
+    </row>
+    <row r="58" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A58" s="6" t="s">
         <v>76</v>
       </c>
       <c r="B58" s="6" t="s">
         <v>13</v>
       </c>
-    </row>
-    <row r="59" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="E58" s="10"/>
+    </row>
+    <row r="59" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A59" s="6" t="s">
         <v>77</v>
       </c>
       <c r="B59" s="6" t="s">
         <v>13</v>
       </c>
-    </row>
-    <row r="60" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="E59" s="10"/>
+    </row>
+    <row r="60" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A60" s="6" t="s">
         <v>78</v>
       </c>
       <c r="B60" s="6" t="s">
         <v>13</v>
       </c>
-    </row>
-    <row r="61" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="E60" s="10"/>
+    </row>
+    <row r="61" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A61" s="6" t="s">
         <v>79</v>
       </c>
       <c r="B61" s="6" t="s">
         <v>13</v>
       </c>
-    </row>
-    <row r="62" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="E61" s="10"/>
+    </row>
+    <row r="62" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A62" s="6" t="s">
         <v>80</v>
       </c>
       <c r="B62" s="6" t="s">
         <v>32</v>
       </c>
-    </row>
-    <row r="63" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="E62" s="10"/>
+    </row>
+    <row r="63" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A63" s="6" t="s">
         <v>81</v>
       </c>
       <c r="B63" s="6" t="s">
         <v>13</v>
       </c>
-    </row>
-    <row r="64" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="E63" s="10"/>
+    </row>
+    <row r="64" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A64" s="6" t="s">
+        <v>113</v>
+      </c>
+      <c r="B64" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="C64" s="6" t="s">
         <v>82</v>
       </c>
-      <c r="B64" s="6" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="65" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="E64" s="10"/>
+    </row>
+    <row r="65" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A65" s="6" t="s">
         <v>83</v>
       </c>
       <c r="B65" s="6" t="s">
         <v>32</v>
       </c>
-    </row>
-    <row r="66" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="E65" s="10"/>
+    </row>
+    <row r="66" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A66" s="6" t="s">
         <v>84</v>
       </c>
       <c r="B66" s="6" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="67" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="E66" s="10"/>
+    </row>
+    <row r="67" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A67" s="6" t="s">
         <v>12</v>
       </c>
       <c r="B67" s="6" t="s">
         <v>13</v>
       </c>
-    </row>
-    <row r="68" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="E67" s="10"/>
+    </row>
+    <row r="68" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A68" s="6" t="s">
         <v>85</v>
       </c>
       <c r="B68" s="6" t="s">
         <v>32</v>
       </c>
-    </row>
-    <row r="69" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="E68" s="10"/>
+    </row>
+    <row r="69" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A69" s="6" t="s">
         <v>86</v>
       </c>
       <c r="B69" s="6" t="s">
         <v>11</v>
       </c>
-    </row>
-    <row r="70" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="E69" s="10"/>
+    </row>
+    <row r="70" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A70" s="6" t="s">
         <v>87</v>
       </c>
       <c r="B70" s="6" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="71" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="E70" s="10"/>
+    </row>
+    <row r="71" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A71" s="6" t="s">
         <v>88</v>
       </c>
       <c r="B71" s="6" t="s">
         <v>32</v>
       </c>
-    </row>
-    <row r="72" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="E71" s="10"/>
+    </row>
+    <row r="72" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A72" s="6" t="s">
         <v>89</v>
       </c>
       <c r="B72" s="6" t="s">
         <v>25</v>
       </c>
-    </row>
-    <row r="73" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="E72" s="10"/>
+    </row>
+    <row r="73" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A73" s="6" t="s">
         <v>90</v>
       </c>
       <c r="B73" s="6" t="s">
         <v>11</v>
       </c>
-    </row>
-    <row r="74" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="E73" s="10"/>
+    </row>
+    <row r="74" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A74" s="6" t="s">
         <v>91</v>
       </c>
       <c r="B74" s="6" t="s">
         <v>11</v>
       </c>
-    </row>
-    <row r="75" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="E74" s="10"/>
+    </row>
+    <row r="75" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A75" s="6" t="s">
         <v>92</v>
       </c>
       <c r="B75" s="6" t="s">
         <v>13</v>
       </c>
-    </row>
-    <row r="76" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="E75" s="10"/>
+    </row>
+    <row r="76" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A76" s="6" t="s">
         <v>93</v>
       </c>
       <c r="B76" s="6" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="77" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="E76" s="10"/>
+    </row>
+    <row r="77" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A77" s="6" t="s">
         <v>94</v>
       </c>
       <c r="B77" s="6" t="s">
         <v>32</v>
       </c>
-    </row>
-    <row r="78" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="E77" s="10"/>
+    </row>
+    <row r="78" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A78" s="6" t="s">
         <v>95</v>
       </c>
       <c r="B78" s="6" t="s">
         <v>11</v>
       </c>
+      <c r="E78" s="10"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/crop_area_by_provinces_TEMPLATE.xlsx
+++ b/crop_area_by_provinces_TEMPLATE.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/pongthanatburanachon/Desktop/work/dashboard/crop_timeline/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BE7E8804-63C1-D045-ACF9-5C87B670DB57}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4E1281B9-46EB-3B49-BC32-16E64D5E8333}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="38400" yWindow="-3760" windowWidth="30240" windowHeight="18880" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="45180" yWindow="-3520" windowWidth="30240" windowHeight="18880" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="crop_area_by_provinces" sheetId="1" r:id="rId1"/>
@@ -458,7 +458,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="11">
+  <cellXfs count="10">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -469,7 +469,6 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="3" fontId="2" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
-    <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="1" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="1"/>
   </cellXfs>
@@ -885,7 +884,7 @@
     </row>
     <row r="4" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A4" s="3" t="s">
-        <v>39</v>
+        <v>26</v>
       </c>
       <c r="B4" s="3" t="s">
         <v>8</v>
@@ -899,7 +898,7 @@
       <c r="E4" s="3">
         <v>2025</v>
       </c>
-      <c r="F4" s="8">
+      <c r="F4" s="7">
         <v>58745</v>
       </c>
       <c r="G4" s="7">
@@ -926,10 +925,10 @@
       <c r="E5" s="3">
         <v>2025</v>
       </c>
-      <c r="F5" s="8">
+      <c r="F5" s="7">
         <v>1261465</v>
       </c>
-      <c r="G5" s="8">
+      <c r="G5" s="7">
         <v>1109790</v>
       </c>
       <c r="H5" t="s">
@@ -952,10 +951,10 @@
       <c r="E6" s="3">
         <v>2025</v>
       </c>
-      <c r="F6" s="8">
+      <c r="F6" s="7">
         <v>622244</v>
       </c>
-      <c r="G6" s="8">
+      <c r="G6" s="7">
         <v>559308</v>
       </c>
       <c r="H6" t="s">
@@ -964,7 +963,7 @@
     </row>
     <row r="7" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A7" s="3" t="s">
-        <v>39</v>
+        <v>26</v>
       </c>
       <c r="B7" s="3" t="s">
         <v>8</v>
@@ -978,10 +977,10 @@
       <c r="E7" s="3">
         <v>2025</v>
       </c>
-      <c r="F7" s="8">
+      <c r="F7" s="7">
         <v>436118</v>
       </c>
-      <c r="G7" s="8">
+      <c r="G7" s="7">
         <v>425641</v>
       </c>
       <c r="H7" t="s">
@@ -1054,19 +1053,19 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A1" s="9" t="s">
+      <c r="A1" s="8" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="9" t="s">
+      <c r="B1" s="8" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="9" t="s">
+      <c r="C1" s="8" t="s">
         <v>14</v>
       </c>
-      <c r="D1" s="9" t="s">
+      <c r="D1" s="8" t="s">
         <v>15</v>
       </c>
-      <c r="E1" s="9" t="s">
+      <c r="E1" s="8" t="s">
         <v>98</v>
       </c>
       <c r="F1" s="5" t="s">
@@ -1083,7 +1082,7 @@
       <c r="C2" s="6" t="s">
         <v>17</v>
       </c>
-      <c r="E2" s="10"/>
+      <c r="E2" s="9"/>
       <c r="F2" s="5" t="s">
         <v>18</v>
       </c>
@@ -1095,7 +1094,7 @@
       <c r="B3" s="6" t="s">
         <v>11</v>
       </c>
-      <c r="E3" s="10"/>
+      <c r="E3" s="9"/>
       <c r="F3" s="5" t="s">
         <v>20</v>
       </c>
@@ -1107,7 +1106,7 @@
       <c r="B4" s="6" t="s">
         <v>13</v>
       </c>
-      <c r="E4" s="10"/>
+      <c r="E4" s="9"/>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A5" s="6" t="s">
@@ -1116,7 +1115,7 @@
       <c r="B5" s="6" t="s">
         <v>11</v>
       </c>
-      <c r="E5" s="10"/>
+      <c r="E5" s="9"/>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A6" s="6" t="s">
@@ -1128,7 +1127,7 @@
       <c r="C6" s="6" t="s">
         <v>23</v>
       </c>
-      <c r="E6" s="10"/>
+      <c r="E6" s="9"/>
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A7" s="6" t="s">
@@ -1137,7 +1136,7 @@
       <c r="B7" s="6" t="s">
         <v>25</v>
       </c>
-      <c r="E7" s="10"/>
+      <c r="E7" s="9"/>
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A8" s="6" t="s">
@@ -1146,7 +1145,7 @@
       <c r="B8" s="6" t="s">
         <v>13</v>
       </c>
-      <c r="E8" s="10"/>
+      <c r="E8" s="9"/>
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A9" s="6" t="s">
@@ -1155,7 +1154,7 @@
       <c r="B9" s="6" t="s">
         <v>11</v>
       </c>
-      <c r="E9" s="10"/>
+      <c r="E9" s="9"/>
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A10" s="6" t="s">
@@ -1164,7 +1163,7 @@
       <c r="B10" s="6" t="s">
         <v>25</v>
       </c>
-      <c r="E10" s="10"/>
+      <c r="E10" s="9"/>
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A11" s="6" t="s">
@@ -1173,7 +1172,7 @@
       <c r="B11" s="6" t="s">
         <v>8</v>
       </c>
-      <c r="E11" s="10"/>
+      <c r="E11" s="9"/>
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A12" s="6" t="s">
@@ -1182,7 +1181,7 @@
       <c r="B12" s="6" t="s">
         <v>8</v>
       </c>
-      <c r="E12" s="10"/>
+      <c r="E12" s="9"/>
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A13" s="6" t="s">
@@ -1194,7 +1193,7 @@
       <c r="C13" s="6" t="s">
         <v>30</v>
       </c>
-      <c r="E13" s="10"/>
+      <c r="E13" s="9"/>
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A14" s="6" t="s">
@@ -1203,7 +1202,7 @@
       <c r="B14" s="6" t="s">
         <v>32</v>
       </c>
-      <c r="E14" s="10"/>
+      <c r="E14" s="9"/>
     </row>
     <row r="15" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A15" s="6" t="s">
@@ -1212,7 +1211,7 @@
       <c r="B15" s="6" t="s">
         <v>11</v>
       </c>
-      <c r="E15" s="10"/>
+      <c r="E15" s="9"/>
     </row>
     <row r="16" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A16" s="6" t="s">
@@ -1221,7 +1220,7 @@
       <c r="B16" s="6" t="s">
         <v>8</v>
       </c>
-      <c r="E16" s="10"/>
+      <c r="E16" s="9"/>
     </row>
     <row r="17" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A17" s="6" t="s">
@@ -1230,7 +1229,7 @@
       <c r="B17" s="6" t="s">
         <v>36</v>
       </c>
-      <c r="E17" s="10"/>
+      <c r="E17" s="9"/>
     </row>
     <row r="18" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A18" s="6" t="s">
@@ -1239,7 +1238,7 @@
       <c r="B18" s="6" t="s">
         <v>11</v>
       </c>
-      <c r="E18" s="10"/>
+      <c r="E18" s="9"/>
     </row>
     <row r="19" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A19" s="6" t="s">
@@ -1248,7 +1247,7 @@
       <c r="B19" s="6" t="s">
         <v>32</v>
       </c>
-      <c r="E19" s="10"/>
+      <c r="E19" s="9"/>
     </row>
     <row r="20" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A20" s="6" t="s">
@@ -1257,7 +1256,7 @@
       <c r="B20" s="6" t="s">
         <v>8</v>
       </c>
-      <c r="E20" s="10"/>
+      <c r="E20" s="9"/>
     </row>
     <row r="21" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A21" s="6" t="s">
@@ -1266,7 +1265,7 @@
       <c r="B21" s="6" t="s">
         <v>8</v>
       </c>
-      <c r="E21" s="10"/>
+      <c r="E21" s="9"/>
     </row>
     <row r="22" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A22" s="6" t="s">
@@ -1275,7 +1274,7 @@
       <c r="B22" s="6" t="s">
         <v>11</v>
       </c>
-      <c r="E22" s="10"/>
+      <c r="E22" s="9"/>
     </row>
     <row r="23" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A23" s="6" t="s">
@@ -1287,7 +1286,7 @@
       <c r="C23" s="6" t="s">
         <v>42</v>
       </c>
-      <c r="E23" s="10"/>
+      <c r="E23" s="9"/>
     </row>
     <row r="24" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A24" s="6" t="s">
@@ -1296,7 +1295,7 @@
       <c r="B24" s="6" t="s">
         <v>8</v>
       </c>
-      <c r="E24" s="10"/>
+      <c r="E24" s="9"/>
     </row>
     <row r="25" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A25" s="6" t="s">
@@ -1305,7 +1304,7 @@
       <c r="B25" s="6" t="s">
         <v>11</v>
       </c>
-      <c r="E25" s="10"/>
+      <c r="E25" s="9"/>
     </row>
     <row r="26" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A26" s="6" t="s">
@@ -1314,7 +1313,7 @@
       <c r="B26" s="6" t="s">
         <v>11</v>
       </c>
-      <c r="E26" s="10"/>
+      <c r="E26" s="9"/>
     </row>
     <row r="27" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A27" s="6" t="s">
@@ -1323,7 +1322,7 @@
       <c r="B27" s="6" t="s">
         <v>13</v>
       </c>
-      <c r="E27" s="10"/>
+      <c r="E27" s="9"/>
     </row>
     <row r="28" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A28" s="6" t="s">
@@ -1332,7 +1331,7 @@
       <c r="B28" s="6" t="s">
         <v>13</v>
       </c>
-      <c r="E28" s="10"/>
+      <c r="E28" s="9"/>
     </row>
     <row r="29" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A29" s="6" t="s">
@@ -1341,7 +1340,7 @@
       <c r="B29" s="6" t="s">
         <v>11</v>
       </c>
-      <c r="E29" s="10"/>
+      <c r="E29" s="9"/>
     </row>
     <row r="30" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A30" s="6" t="s">
@@ -1350,7 +1349,7 @@
       <c r="B30" s="6" t="s">
         <v>11</v>
       </c>
-      <c r="E30" s="10"/>
+      <c r="E30" s="9"/>
     </row>
     <row r="31" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A31" s="6" t="s">
@@ -1359,7 +1358,7 @@
       <c r="B31" s="6" t="s">
         <v>13</v>
       </c>
-      <c r="E31" s="10"/>
+      <c r="E31" s="9"/>
     </row>
     <row r="32" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A32" s="6" t="s">
@@ -1368,7 +1367,7 @@
       <c r="B32" s="6" t="s">
         <v>32</v>
       </c>
-      <c r="E32" s="10"/>
+      <c r="E32" s="9"/>
     </row>
     <row r="33" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A33" s="6" t="s">
@@ -1377,7 +1376,7 @@
       <c r="B33" s="6" t="s">
         <v>8</v>
       </c>
-      <c r="E33" s="10"/>
+      <c r="E33" s="9"/>
     </row>
     <row r="34" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A34" s="6" t="s">
@@ -1386,7 +1385,7 @@
       <c r="B34" s="6" t="s">
         <v>32</v>
       </c>
-      <c r="E34" s="10"/>
+      <c r="E34" s="9"/>
     </row>
     <row r="35" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A35" s="6" t="s">
@@ -1398,7 +1397,7 @@
       <c r="C35" s="6" t="s">
         <v>53</v>
       </c>
-      <c r="E35" s="10"/>
+      <c r="E35" s="9"/>
     </row>
     <row r="36" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A36" s="6" t="s">
@@ -1407,7 +1406,7 @@
       <c r="B36" s="6" t="s">
         <v>11</v>
       </c>
-      <c r="E36" s="10"/>
+      <c r="E36" s="9"/>
     </row>
     <row r="37" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A37" s="6" t="s">
@@ -1416,7 +1415,7 @@
       <c r="B37" s="6" t="s">
         <v>13</v>
       </c>
-      <c r="E37" s="10"/>
+      <c r="E37" s="9"/>
     </row>
     <row r="38" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A38" s="6" t="s">
@@ -1425,7 +1424,7 @@
       <c r="B38" s="6" t="s">
         <v>13</v>
       </c>
-      <c r="E38" s="10"/>
+      <c r="E38" s="9"/>
     </row>
     <row r="39" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A39" s="6" t="s">
@@ -1434,7 +1433,7 @@
       <c r="B39" s="6" t="s">
         <v>32</v>
       </c>
-      <c r="E39" s="10"/>
+      <c r="E39" s="9"/>
     </row>
     <row r="40" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A40" s="6" t="s">
@@ -1446,7 +1445,7 @@
       <c r="C40" s="6" t="s">
         <v>58</v>
       </c>
-      <c r="E40" s="10"/>
+      <c r="E40" s="9"/>
     </row>
     <row r="41" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A41" s="6" t="s">
@@ -1455,7 +1454,7 @@
       <c r="B41" s="6" t="s">
         <v>32</v>
       </c>
-      <c r="E41" s="10"/>
+      <c r="E41" s="9"/>
     </row>
     <row r="42" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A42" s="6" t="s">
@@ -1464,7 +1463,7 @@
       <c r="B42" s="6" t="s">
         <v>8</v>
       </c>
-      <c r="E42" s="10"/>
+      <c r="E42" s="9"/>
     </row>
     <row r="43" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A43" s="6" t="s">
@@ -1473,7 +1472,7 @@
       <c r="B43" s="6" t="s">
         <v>13</v>
       </c>
-      <c r="E43" s="10"/>
+      <c r="E43" s="9"/>
     </row>
     <row r="44" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A44" s="6" t="s">
@@ -1482,7 +1481,7 @@
       <c r="B44" s="6" t="s">
         <v>36</v>
       </c>
-      <c r="E44" s="10"/>
+      <c r="E44" s="9"/>
     </row>
     <row r="45" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A45" s="6" t="s">
@@ -1491,7 +1490,7 @@
       <c r="B45" s="6" t="s">
         <v>13</v>
       </c>
-      <c r="E45" s="10"/>
+      <c r="E45" s="9"/>
     </row>
     <row r="46" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A46" s="6" t="s">
@@ -1500,7 +1499,7 @@
       <c r="B46" s="6" t="s">
         <v>8</v>
       </c>
-      <c r="E46" s="10"/>
+      <c r="E46" s="9"/>
     </row>
     <row r="47" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A47" s="6" t="s">
@@ -1509,7 +1508,7 @@
       <c r="B47" s="6" t="s">
         <v>13</v>
       </c>
-      <c r="E47" s="10"/>
+      <c r="E47" s="9"/>
     </row>
     <row r="48" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A48" s="6" t="s">
@@ -1518,7 +1517,7 @@
       <c r="B48" s="6" t="s">
         <v>8</v>
       </c>
-      <c r="E48" s="10"/>
+      <c r="E48" s="9"/>
     </row>
     <row r="49" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A49" s="6" t="s">
@@ -1527,7 +1526,7 @@
       <c r="B49" s="6" t="s">
         <v>32</v>
       </c>
-      <c r="E49" s="10"/>
+      <c r="E49" s="9"/>
     </row>
     <row r="50" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A50" s="6" t="s">
@@ -1539,7 +1538,7 @@
       <c r="C50" s="6" t="s">
         <v>68</v>
       </c>
-      <c r="E50" s="10"/>
+      <c r="E50" s="9"/>
     </row>
     <row r="51" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A51" s="6" t="s">
@@ -1548,7 +1547,7 @@
       <c r="B51" s="6" t="s">
         <v>36</v>
       </c>
-      <c r="E51" s="10"/>
+      <c r="E51" s="9"/>
     </row>
     <row r="52" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A52" s="6" t="s">
@@ -1557,7 +1556,7 @@
       <c r="B52" s="6" t="s">
         <v>32</v>
       </c>
-      <c r="E52" s="10"/>
+      <c r="E52" s="9"/>
     </row>
     <row r="53" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A53" s="6" t="s">
@@ -1566,7 +1565,7 @@
       <c r="B53" s="6" t="s">
         <v>36</v>
       </c>
-      <c r="E53" s="10"/>
+      <c r="E53" s="9"/>
     </row>
     <row r="54" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A54" s="6" t="s">
@@ -1575,7 +1574,7 @@
       <c r="B54" s="6" t="s">
         <v>25</v>
       </c>
-      <c r="E54" s="10"/>
+      <c r="E54" s="9"/>
     </row>
     <row r="55" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A55" s="6" t="s">
@@ -1584,7 +1583,7 @@
       <c r="B55" s="6" t="s">
         <v>11</v>
       </c>
-      <c r="E55" s="10"/>
+      <c r="E55" s="9"/>
     </row>
     <row r="56" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A56" s="6" t="s">
@@ -1593,7 +1592,7 @@
       <c r="B56" s="6" t="s">
         <v>25</v>
       </c>
-      <c r="E56" s="10"/>
+      <c r="E56" s="9"/>
     </row>
     <row r="57" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A57" s="6" t="s">
@@ -1602,7 +1601,7 @@
       <c r="B57" s="6" t="s">
         <v>11</v>
       </c>
-      <c r="E57" s="10"/>
+      <c r="E57" s="9"/>
     </row>
     <row r="58" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A58" s="6" t="s">
@@ -1611,7 +1610,7 @@
       <c r="B58" s="6" t="s">
         <v>13</v>
       </c>
-      <c r="E58" s="10"/>
+      <c r="E58" s="9"/>
     </row>
     <row r="59" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A59" s="6" t="s">
@@ -1620,7 +1619,7 @@
       <c r="B59" s="6" t="s">
         <v>13</v>
       </c>
-      <c r="E59" s="10"/>
+      <c r="E59" s="9"/>
     </row>
     <row r="60" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A60" s="6" t="s">
@@ -1629,7 +1628,7 @@
       <c r="B60" s="6" t="s">
         <v>13</v>
       </c>
-      <c r="E60" s="10"/>
+      <c r="E60" s="9"/>
     </row>
     <row r="61" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A61" s="6" t="s">
@@ -1638,7 +1637,7 @@
       <c r="B61" s="6" t="s">
         <v>13</v>
       </c>
-      <c r="E61" s="10"/>
+      <c r="E61" s="9"/>
     </row>
     <row r="62" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A62" s="6" t="s">
@@ -1647,7 +1646,7 @@
       <c r="B62" s="6" t="s">
         <v>32</v>
       </c>
-      <c r="E62" s="10"/>
+      <c r="E62" s="9"/>
     </row>
     <row r="63" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A63" s="6" t="s">
@@ -1656,7 +1655,7 @@
       <c r="B63" s="6" t="s">
         <v>13</v>
       </c>
-      <c r="E63" s="10"/>
+      <c r="E63" s="9"/>
     </row>
     <row r="64" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A64" s="6" t="s">
@@ -1668,7 +1667,7 @@
       <c r="C64" s="6" t="s">
         <v>82</v>
       </c>
-      <c r="E64" s="10"/>
+      <c r="E64" s="9"/>
     </row>
     <row r="65" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A65" s="6" t="s">
@@ -1677,7 +1676,7 @@
       <c r="B65" s="6" t="s">
         <v>32</v>
       </c>
-      <c r="E65" s="10"/>
+      <c r="E65" s="9"/>
     </row>
     <row r="66" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A66" s="6" t="s">
@@ -1686,7 +1685,7 @@
       <c r="B66" s="6" t="s">
         <v>8</v>
       </c>
-      <c r="E66" s="10"/>
+      <c r="E66" s="9"/>
     </row>
     <row r="67" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A67" s="6" t="s">
@@ -1695,7 +1694,7 @@
       <c r="B67" s="6" t="s">
         <v>13</v>
       </c>
-      <c r="E67" s="10"/>
+      <c r="E67" s="9"/>
     </row>
     <row r="68" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A68" s="6" t="s">
@@ -1704,7 +1703,7 @@
       <c r="B68" s="6" t="s">
         <v>32</v>
       </c>
-      <c r="E68" s="10"/>
+      <c r="E68" s="9"/>
     </row>
     <row r="69" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A69" s="6" t="s">
@@ -1713,7 +1712,7 @@
       <c r="B69" s="6" t="s">
         <v>11</v>
       </c>
-      <c r="E69" s="10"/>
+      <c r="E69" s="9"/>
     </row>
     <row r="70" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A70" s="6" t="s">
@@ -1722,7 +1721,7 @@
       <c r="B70" s="6" t="s">
         <v>8</v>
       </c>
-      <c r="E70" s="10"/>
+      <c r="E70" s="9"/>
     </row>
     <row r="71" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A71" s="6" t="s">
@@ -1731,7 +1730,7 @@
       <c r="B71" s="6" t="s">
         <v>32</v>
       </c>
-      <c r="E71" s="10"/>
+      <c r="E71" s="9"/>
     </row>
     <row r="72" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A72" s="6" t="s">
@@ -1740,7 +1739,7 @@
       <c r="B72" s="6" t="s">
         <v>25</v>
       </c>
-      <c r="E72" s="10"/>
+      <c r="E72" s="9"/>
     </row>
     <row r="73" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A73" s="6" t="s">
@@ -1749,7 +1748,7 @@
       <c r="B73" s="6" t="s">
         <v>11</v>
       </c>
-      <c r="E73" s="10"/>
+      <c r="E73" s="9"/>
     </row>
     <row r="74" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A74" s="6" t="s">
@@ -1758,7 +1757,7 @@
       <c r="B74" s="6" t="s">
         <v>11</v>
       </c>
-      <c r="E74" s="10"/>
+      <c r="E74" s="9"/>
     </row>
     <row r="75" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A75" s="6" t="s">
@@ -1767,7 +1766,7 @@
       <c r="B75" s="6" t="s">
         <v>13</v>
       </c>
-      <c r="E75" s="10"/>
+      <c r="E75" s="9"/>
     </row>
     <row r="76" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A76" s="6" t="s">
@@ -1776,7 +1775,7 @@
       <c r="B76" s="6" t="s">
         <v>8</v>
       </c>
-      <c r="E76" s="10"/>
+      <c r="E76" s="9"/>
     </row>
     <row r="77" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A77" s="6" t="s">
@@ -1785,7 +1784,7 @@
       <c r="B77" s="6" t="s">
         <v>32</v>
       </c>
-      <c r="E77" s="10"/>
+      <c r="E77" s="9"/>
     </row>
     <row r="78" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A78" s="6" t="s">
@@ -1794,7 +1793,7 @@
       <c r="B78" s="6" t="s">
         <v>11</v>
       </c>
-      <c r="E78" s="10"/>
+      <c r="E78" s="9"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/crop_area_by_provinces_TEMPLATE.xlsx
+++ b/crop_area_by_provinces_TEMPLATE.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/pongthanatburanachon/Desktop/work/dashboard/crop_timeline/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4E1281B9-46EB-3B49-BC32-16E64D5E8333}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2DBBE3CB-5EC8-6D44-9A8D-71F8D4E6F0CF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="45180" yWindow="-3520" windowWidth="30240" windowHeight="18880" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="38400" yWindow="-4660" windowWidth="30240" windowHeight="18880" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="crop_area_by_provinces" sheetId="1" r:id="rId1"/>
@@ -884,7 +884,7 @@
     </row>
     <row r="4" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A4" s="3" t="s">
-        <v>26</v>
+        <v>39</v>
       </c>
       <c r="B4" s="3" t="s">
         <v>8</v>
@@ -963,7 +963,7 @@
     </row>
     <row r="7" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A7" s="3" t="s">
-        <v>26</v>
+        <v>39</v>
       </c>
       <c r="B7" s="3" t="s">
         <v>8</v>

--- a/crop_area_by_provinces_TEMPLATE.xlsx
+++ b/crop_area_by_provinces_TEMPLATE.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/pongthanatburanachon/Desktop/work/dashboard/crop_timeline/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2DBBE3CB-5EC8-6D44-9A8D-71F8D4E6F0CF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4DA265A8-FAEF-C44C-9C96-749078910D0A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="38400" yWindow="-4660" windowWidth="30240" windowHeight="18880" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -152,229 +152,229 @@
     <t>Krabi</t>
   </si>
   <si>
+    <t>Lamphun</t>
+  </si>
+  <si>
+    <t>Loei</t>
+  </si>
+  <si>
+    <t>Lopburi</t>
+  </si>
+  <si>
+    <t>Mae Hong Son</t>
+  </si>
+  <si>
+    <t>Maha Sarakham</t>
+  </si>
+  <si>
+    <t>Mukdahan</t>
+  </si>
+  <si>
+    <t>Nakhon Nayok</t>
+  </si>
+  <si>
+    <t>Nakhon Pathom</t>
+  </si>
+  <si>
+    <t>Nakhon Phanom</t>
+  </si>
+  <si>
+    <t>Nakhon Sawan</t>
+  </si>
+  <si>
+    <t>Nakhon Si Thammarat</t>
+  </si>
+  <si>
+    <t>Nan</t>
+  </si>
+  <si>
+    <t>Narathiwat</t>
+  </si>
+  <si>
+    <t>Nong Bua Lamphu</t>
+  </si>
+  <si>
+    <t>Nong Khai</t>
+  </si>
+  <si>
+    <t>Nonthaburi</t>
+  </si>
+  <si>
+    <t>Pathum Thani</t>
+  </si>
+  <si>
+    <t>Pattani</t>
+  </si>
+  <si>
+    <t>Phang Nga</t>
+  </si>
+  <si>
+    <t>Phatthalung</t>
+  </si>
+  <si>
+    <t>Phayao</t>
+  </si>
+  <si>
+    <t>Phetchabun</t>
+  </si>
+  <si>
+    <t>Phetchaburi</t>
+  </si>
+  <si>
+    <t>Phichit</t>
+  </si>
+  <si>
+    <t>Phitsanulok</t>
+  </si>
+  <si>
+    <t>Phra Nakhon Si Ayutthaya</t>
+  </si>
+  <si>
+    <t>Phrae</t>
+  </si>
+  <si>
+    <t>Phuket</t>
+  </si>
+  <si>
+    <t>Prachinburi</t>
+  </si>
+  <si>
+    <t>Prachuap Khiri Khan</t>
+  </si>
+  <si>
+    <t>Ranong</t>
+  </si>
+  <si>
+    <t>Ratchaburi</t>
+  </si>
+  <si>
+    <t>Rayong</t>
+  </si>
+  <si>
+    <t>Roi Et</t>
+  </si>
+  <si>
+    <t>Sa Kaeo</t>
+  </si>
+  <si>
+    <t>Sakon Nakhon</t>
+  </si>
+  <si>
+    <t>Samut Prakan</t>
+  </si>
+  <si>
+    <t>Samut Sakhon</t>
+  </si>
+  <si>
+    <t>Samut Songkhram</t>
+  </si>
+  <si>
+    <t>Saraburi</t>
+  </si>
+  <si>
+    <t>Satun</t>
+  </si>
+  <si>
+    <t>Sing Buri</t>
+  </si>
+  <si>
+    <t>Sisaket</t>
+  </si>
+  <si>
+    <t>Songkhla</t>
+  </si>
+  <si>
+    <t>Sukhothai</t>
+  </si>
+  <si>
+    <t>Surat Thani</t>
+  </si>
+  <si>
+    <t>Surin</t>
+  </si>
+  <si>
+    <t>Tak</t>
+  </si>
+  <si>
+    <t>Trang</t>
+  </si>
+  <si>
+    <t>Trat</t>
+  </si>
+  <si>
+    <t>Ubon Ratchathani</t>
+  </si>
+  <si>
+    <t>Udon Thani</t>
+  </si>
+  <si>
+    <t>Uthai Thani</t>
+  </si>
+  <si>
+    <t>Uttaradit</t>
+  </si>
+  <si>
+    <t>Yala</t>
+  </si>
+  <si>
+    <t>Yasothon</t>
+  </si>
+  <si>
+    <t>off season rice</t>
+  </si>
+  <si>
+    <t>in season rice</t>
+  </si>
+  <si>
+    <t>SHK_region</t>
+  </si>
+  <si>
+    <t>R1</t>
+  </si>
+  <si>
+    <t>R2</t>
+  </si>
+  <si>
+    <t>R3</t>
+  </si>
+  <si>
+    <t>fertilizer_usage</t>
+  </si>
+  <si>
+    <t>herbicide_usage</t>
+  </si>
+  <si>
+    <t>insecticide_usage</t>
+  </si>
+  <si>
+    <t>fungicide_usage</t>
+  </si>
+  <si>
+    <t>Bangkok Metropolis</t>
+  </si>
+  <si>
+    <t>Buri Ram</t>
+  </si>
+  <si>
+    <t>Chon Buri</t>
+  </si>
+  <si>
+    <t>Lop Buri</t>
+  </si>
+  <si>
+    <t>Nong Bua Lam Phu</t>
+  </si>
+  <si>
+    <t>Phangnga</t>
+  </si>
+  <si>
+    <t>Prachin Buri</t>
+  </si>
+  <si>
+    <t>Si Sa Ket</t>
+  </si>
+  <si>
     <t>Lampang</t>
-  </si>
-  <si>
-    <t>Lamphun</t>
-  </si>
-  <si>
-    <t>Loei</t>
-  </si>
-  <si>
-    <t>Lopburi</t>
-  </si>
-  <si>
-    <t>Mae Hong Son</t>
-  </si>
-  <si>
-    <t>Maha Sarakham</t>
-  </si>
-  <si>
-    <t>Mukdahan</t>
-  </si>
-  <si>
-    <t>Nakhon Nayok</t>
-  </si>
-  <si>
-    <t>Nakhon Pathom</t>
-  </si>
-  <si>
-    <t>Nakhon Phanom</t>
-  </si>
-  <si>
-    <t>Nakhon Sawan</t>
-  </si>
-  <si>
-    <t>Nakhon Si Thammarat</t>
-  </si>
-  <si>
-    <t>Nan</t>
-  </si>
-  <si>
-    <t>Narathiwat</t>
-  </si>
-  <si>
-    <t>Nong Bua Lamphu</t>
-  </si>
-  <si>
-    <t>Nong Khai</t>
-  </si>
-  <si>
-    <t>Nonthaburi</t>
-  </si>
-  <si>
-    <t>Pathum Thani</t>
-  </si>
-  <si>
-    <t>Pattani</t>
-  </si>
-  <si>
-    <t>Phang Nga</t>
-  </si>
-  <si>
-    <t>Phatthalung</t>
-  </si>
-  <si>
-    <t>Phayao</t>
-  </si>
-  <si>
-    <t>Phetchabun</t>
-  </si>
-  <si>
-    <t>Phetchaburi</t>
-  </si>
-  <si>
-    <t>Phichit</t>
-  </si>
-  <si>
-    <t>Phitsanulok</t>
-  </si>
-  <si>
-    <t>Phra Nakhon Si Ayutthaya</t>
-  </si>
-  <si>
-    <t>Phrae</t>
-  </si>
-  <si>
-    <t>Phuket</t>
-  </si>
-  <si>
-    <t>Prachinburi</t>
-  </si>
-  <si>
-    <t>Prachuap Khiri Khan</t>
-  </si>
-  <si>
-    <t>Ranong</t>
-  </si>
-  <si>
-    <t>Ratchaburi</t>
-  </si>
-  <si>
-    <t>Rayong</t>
-  </si>
-  <si>
-    <t>Roi Et</t>
-  </si>
-  <si>
-    <t>Sa Kaeo</t>
-  </si>
-  <si>
-    <t>Sakon Nakhon</t>
-  </si>
-  <si>
-    <t>Samut Prakan</t>
-  </si>
-  <si>
-    <t>Samut Sakhon</t>
-  </si>
-  <si>
-    <t>Samut Songkhram</t>
-  </si>
-  <si>
-    <t>Saraburi</t>
-  </si>
-  <si>
-    <t>Satun</t>
-  </si>
-  <si>
-    <t>Sing Buri</t>
-  </si>
-  <si>
-    <t>Sisaket</t>
-  </si>
-  <si>
-    <t>Songkhla</t>
-  </si>
-  <si>
-    <t>Sukhothai</t>
-  </si>
-  <si>
-    <t>Surat Thani</t>
-  </si>
-  <si>
-    <t>Surin</t>
-  </si>
-  <si>
-    <t>Tak</t>
-  </si>
-  <si>
-    <t>Trang</t>
-  </si>
-  <si>
-    <t>Trat</t>
-  </si>
-  <si>
-    <t>Ubon Ratchathani</t>
-  </si>
-  <si>
-    <t>Udon Thani</t>
-  </si>
-  <si>
-    <t>Uthai Thani</t>
-  </si>
-  <si>
-    <t>Uttaradit</t>
-  </si>
-  <si>
-    <t>Yala</t>
-  </si>
-  <si>
-    <t>Yasothon</t>
-  </si>
-  <si>
-    <t>off season rice</t>
-  </si>
-  <si>
-    <t>in season rice</t>
-  </si>
-  <si>
-    <t>SHK_region</t>
-  </si>
-  <si>
-    <t>R1</t>
-  </si>
-  <si>
-    <t>R2</t>
-  </si>
-  <si>
-    <t>R3</t>
-  </si>
-  <si>
-    <t>fertilizer_usage</t>
-  </si>
-  <si>
-    <t>herbicide_usage</t>
-  </si>
-  <si>
-    <t>insecticide_usage</t>
-  </si>
-  <si>
-    <t>fungicide_usage</t>
-  </si>
-  <si>
-    <t>Bangkok Metropolis</t>
-  </si>
-  <si>
-    <t>Buri Ram</t>
-  </si>
-  <si>
-    <t>Chon Buri</t>
-  </si>
-  <si>
-    <t>Lop Buri</t>
-  </si>
-  <si>
-    <t>Nong Bua Lam Phu</t>
-  </si>
-  <si>
-    <t>Phangnga</t>
-  </si>
-  <si>
-    <t>Prachin Buri</t>
-  </si>
-  <si>
-    <t>Si Sa Ket</t>
   </si>
 </sst>
 </file>
@@ -813,19 +813,19 @@
         <v>6</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="I1" s="2" t="s">
+        <v>101</v>
+      </c>
+      <c r="J1" s="1" t="s">
         <v>102</v>
       </c>
-      <c r="J1" s="1" t="s">
+      <c r="K1" s="1" t="s">
         <v>103</v>
       </c>
-      <c r="K1" s="1" t="s">
+      <c r="L1" s="1" t="s">
         <v>104</v>
-      </c>
-      <c r="L1" s="1" t="s">
-        <v>105</v>
       </c>
     </row>
     <row r="2" spans="1:12" x14ac:dyDescent="0.2">
@@ -836,7 +836,7 @@
         <v>8</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="D2" s="3" t="s">
         <v>9</v>
@@ -851,19 +851,19 @@
         <v>508845</v>
       </c>
       <c r="H2" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="I2" s="4"/>
     </row>
     <row r="3" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A3" s="3" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="B3" s="3" t="s">
         <v>8</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="D3" s="3" t="s">
         <v>9</v>
@@ -878,19 +878,19 @@
         <v>95378</v>
       </c>
       <c r="H3" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="I3" s="4"/>
     </row>
     <row r="4" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A4" s="3" t="s">
-        <v>39</v>
+        <v>113</v>
       </c>
       <c r="B4" s="3" t="s">
         <v>8</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="D4" s="3" t="s">
         <v>9</v>
@@ -905,7 +905,7 @@
         <v>58624</v>
       </c>
       <c r="H4" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="I4" s="4"/>
     </row>
@@ -917,7 +917,7 @@
         <v>8</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="D5" s="3" t="s">
         <v>9</v>
@@ -932,18 +932,18 @@
         <v>1109790</v>
       </c>
       <c r="H5" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
     </row>
     <row r="6" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A6" s="3" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="B6" s="3" t="s">
         <v>8</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="D6" s="3" t="s">
         <v>9</v>
@@ -958,12 +958,12 @@
         <v>559308</v>
       </c>
       <c r="H6" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
     </row>
     <row r="7" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A7" s="3" t="s">
-        <v>39</v>
+        <v>113</v>
       </c>
       <c r="B7" s="3" t="s">
         <v>8</v>
@@ -984,7 +984,7 @@
         <v>425641</v>
       </c>
       <c r="H7" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
     </row>
     <row r="8" spans="1:12" x14ac:dyDescent="0.2">
@@ -1066,7 +1066,7 @@
         <v>15</v>
       </c>
       <c r="E1" s="8" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="F1" s="5" t="s">
         <v>16</v>
@@ -1074,7 +1074,7 @@
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A2" s="6" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="B2" s="6" t="s">
         <v>13</v>
@@ -1119,7 +1119,7 @@
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A6" s="6" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="B6" s="6" t="s">
         <v>11</v>
@@ -1185,7 +1185,7 @@
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A13" s="6" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="B13" s="6" t="s">
         <v>25</v>
@@ -1251,7 +1251,7 @@
     </row>
     <row r="20" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A20" s="6" t="s">
-        <v>39</v>
+        <v>113</v>
       </c>
       <c r="B20" s="6" t="s">
         <v>8</v>
@@ -1260,7 +1260,7 @@
     </row>
     <row r="21" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A21" s="6" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="B21" s="6" t="s">
         <v>8</v>
@@ -1269,7 +1269,7 @@
     </row>
     <row r="22" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A22" s="6" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="B22" s="6" t="s">
         <v>11</v>
@@ -1278,19 +1278,19 @@
     </row>
     <row r="23" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A23" s="6" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="B23" s="6" t="s">
         <v>13</v>
       </c>
       <c r="C23" s="6" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="E23" s="9"/>
     </row>
     <row r="24" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A24" s="6" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="B24" s="6" t="s">
         <v>8</v>
@@ -1299,7 +1299,7 @@
     </row>
     <row r="25" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A25" s="6" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="B25" s="6" t="s">
         <v>11</v>
@@ -1308,7 +1308,7 @@
     </row>
     <row r="26" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A26" s="6" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="B26" s="6" t="s">
         <v>11</v>
@@ -1317,7 +1317,7 @@
     </row>
     <row r="27" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A27" s="6" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="B27" s="6" t="s">
         <v>13</v>
@@ -1326,7 +1326,7 @@
     </row>
     <row r="28" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A28" s="6" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="B28" s="6" t="s">
         <v>13</v>
@@ -1335,7 +1335,7 @@
     </row>
     <row r="29" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A29" s="6" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="B29" s="6" t="s">
         <v>11</v>
@@ -1353,7 +1353,7 @@
     </row>
     <row r="31" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A31" s="6" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="B31" s="6" t="s">
         <v>13</v>
@@ -1362,7 +1362,7 @@
     </row>
     <row r="32" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A32" s="6" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="B32" s="6" t="s">
         <v>32</v>
@@ -1371,7 +1371,7 @@
     </row>
     <row r="33" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A33" s="6" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="B33" s="6" t="s">
         <v>8</v>
@@ -1380,7 +1380,7 @@
     </row>
     <row r="34" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A34" s="6" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="B34" s="6" t="s">
         <v>32</v>
@@ -1389,19 +1389,19 @@
     </row>
     <row r="35" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A35" s="6" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="B35" s="6" t="s">
         <v>11</v>
       </c>
       <c r="C35" s="6" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="E35" s="9"/>
     </row>
     <row r="36" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A36" s="6" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="B36" s="6" t="s">
         <v>11</v>
@@ -1410,7 +1410,7 @@
     </row>
     <row r="37" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A37" s="6" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="B37" s="6" t="s">
         <v>13</v>
@@ -1419,7 +1419,7 @@
     </row>
     <row r="38" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A38" s="6" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="B38" s="6" t="s">
         <v>13</v>
@@ -1428,7 +1428,7 @@
     </row>
     <row r="39" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A39" s="6" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="B39" s="6" t="s">
         <v>32</v>
@@ -1437,19 +1437,19 @@
     </row>
     <row r="40" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A40" s="6" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="B40" s="6" t="s">
         <v>32</v>
       </c>
       <c r="C40" s="6" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="E40" s="9"/>
     </row>
     <row r="41" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A41" s="6" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="B41" s="6" t="s">
         <v>32</v>
@@ -1458,7 +1458,7 @@
     </row>
     <row r="42" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A42" s="6" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="B42" s="6" t="s">
         <v>8</v>
@@ -1467,7 +1467,7 @@
     </row>
     <row r="43" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A43" s="6" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="B43" s="6" t="s">
         <v>13</v>
@@ -1476,7 +1476,7 @@
     </row>
     <row r="44" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A44" s="6" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="B44" s="6" t="s">
         <v>36</v>
@@ -1485,7 +1485,7 @@
     </row>
     <row r="45" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A45" s="6" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="B45" s="6" t="s">
         <v>13</v>
@@ -1494,7 +1494,7 @@
     </row>
     <row r="46" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A46" s="6" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="B46" s="6" t="s">
         <v>8</v>
@@ -1503,7 +1503,7 @@
     </row>
     <row r="47" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A47" s="6" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="B47" s="6" t="s">
         <v>13</v>
@@ -1512,7 +1512,7 @@
     </row>
     <row r="48" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A48" s="6" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="B48" s="6" t="s">
         <v>8</v>
@@ -1521,7 +1521,7 @@
     </row>
     <row r="49" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A49" s="6" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="B49" s="6" t="s">
         <v>32</v>
@@ -1530,19 +1530,19 @@
     </row>
     <row r="50" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A50" s="6" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="B50" s="6" t="s">
         <v>25</v>
       </c>
       <c r="C50" s="6" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="E50" s="9"/>
     </row>
     <row r="51" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A51" s="6" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="B51" s="6" t="s">
         <v>36</v>
@@ -1551,7 +1551,7 @@
     </row>
     <row r="52" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A52" s="6" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="B52" s="6" t="s">
         <v>32</v>
@@ -1560,7 +1560,7 @@
     </row>
     <row r="53" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A53" s="6" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="B53" s="6" t="s">
         <v>36</v>
@@ -1569,7 +1569,7 @@
     </row>
     <row r="54" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A54" s="6" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="B54" s="6" t="s">
         <v>25</v>
@@ -1578,7 +1578,7 @@
     </row>
     <row r="55" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A55" s="6" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="B55" s="6" t="s">
         <v>11</v>
@@ -1587,7 +1587,7 @@
     </row>
     <row r="56" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A56" s="6" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="B56" s="6" t="s">
         <v>25</v>
@@ -1596,7 +1596,7 @@
     </row>
     <row r="57" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A57" s="6" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="B57" s="6" t="s">
         <v>11</v>
@@ -1605,7 +1605,7 @@
     </row>
     <row r="58" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A58" s="6" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="B58" s="6" t="s">
         <v>13</v>
@@ -1614,7 +1614,7 @@
     </row>
     <row r="59" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A59" s="6" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="B59" s="6" t="s">
         <v>13</v>
@@ -1623,7 +1623,7 @@
     </row>
     <row r="60" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A60" s="6" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="B60" s="6" t="s">
         <v>13</v>
@@ -1632,7 +1632,7 @@
     </row>
     <row r="61" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A61" s="6" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="B61" s="6" t="s">
         <v>13</v>
@@ -1641,7 +1641,7 @@
     </row>
     <row r="62" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A62" s="6" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="B62" s="6" t="s">
         <v>32</v>
@@ -1650,7 +1650,7 @@
     </row>
     <row r="63" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A63" s="6" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="B63" s="6" t="s">
         <v>13</v>
@@ -1659,19 +1659,19 @@
     </row>
     <row r="64" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A64" s="6" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="B64" s="6" t="s">
         <v>11</v>
       </c>
       <c r="C64" s="6" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="E64" s="9"/>
     </row>
     <row r="65" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A65" s="6" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="B65" s="6" t="s">
         <v>32</v>
@@ -1680,7 +1680,7 @@
     </row>
     <row r="66" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A66" s="6" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="B66" s="6" t="s">
         <v>8</v>
@@ -1698,7 +1698,7 @@
     </row>
     <row r="68" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A68" s="6" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="B68" s="6" t="s">
         <v>32</v>
@@ -1707,7 +1707,7 @@
     </row>
     <row r="69" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A69" s="6" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="B69" s="6" t="s">
         <v>11</v>
@@ -1716,7 +1716,7 @@
     </row>
     <row r="70" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A70" s="6" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="B70" s="6" t="s">
         <v>8</v>
@@ -1725,7 +1725,7 @@
     </row>
     <row r="71" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A71" s="6" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="B71" s="6" t="s">
         <v>32</v>
@@ -1734,7 +1734,7 @@
     </row>
     <row r="72" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A72" s="6" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="B72" s="6" t="s">
         <v>25</v>
@@ -1743,7 +1743,7 @@
     </row>
     <row r="73" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A73" s="6" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="B73" s="6" t="s">
         <v>11</v>
@@ -1752,7 +1752,7 @@
     </row>
     <row r="74" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A74" s="6" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="B74" s="6" t="s">
         <v>11</v>
@@ -1761,7 +1761,7 @@
     </row>
     <row r="75" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A75" s="6" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="B75" s="6" t="s">
         <v>13</v>
@@ -1770,7 +1770,7 @@
     </row>
     <row r="76" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A76" s="6" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="B76" s="6" t="s">
         <v>8</v>
@@ -1779,7 +1779,7 @@
     </row>
     <row r="77" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A77" s="6" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="B77" s="6" t="s">
         <v>32</v>
@@ -1788,7 +1788,7 @@
     </row>
     <row r="78" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A78" s="6" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="B78" s="6" t="s">
         <v>11</v>

--- a/crop_area_by_provinces_TEMPLATE.xlsx
+++ b/crop_area_by_provinces_TEMPLATE.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/pongthanatburanachon/Desktop/work/dashboard/crop_timeline/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4DA265A8-FAEF-C44C-9C96-749078910D0A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{83597994-3587-D046-8D99-93B9C11F0977}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="38400" yWindow="-4660" windowWidth="30240" windowHeight="18880" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="212" uniqueCount="114">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="208" uniqueCount="110">
   <si>
     <t>province_name_en</t>
   </si>
@@ -336,18 +336,6 @@
   </si>
   <si>
     <t>R3</t>
-  </si>
-  <si>
-    <t>fertilizer_usage</t>
-  </si>
-  <si>
-    <t>herbicide_usage</t>
-  </si>
-  <si>
-    <t>insecticide_usage</t>
-  </si>
-  <si>
-    <t>fungicide_usage</t>
   </si>
   <si>
     <t>Bangkok Metropolis</t>
@@ -381,7 +369,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="5" x14ac:knownFonts="1">
+  <fonts count="4" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -397,12 +385,6 @@
       <family val="2"/>
     </font>
     <font>
-      <sz val="11"/>
-      <name val="Arial"/>
-      <family val="2"/>
-    </font>
-    <font>
-      <b/>
       <sz val="11"/>
       <name val="Arial"/>
       <family val="2"/>
@@ -458,15 +440,11 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="10">
+  <cellXfs count="8">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="3" fontId="2" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="1" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
@@ -773,7 +751,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:L19"/>
+  <dimension ref="A1:H19"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="20" customWidth="1"/>
@@ -784,13 +762,9 @@
     <col min="6" max="6" width="16" customWidth="1"/>
     <col min="7" max="7" width="18" customWidth="1"/>
     <col min="8" max="8" width="13.33203125" customWidth="1"/>
-    <col min="9" max="9" width="15.6640625" customWidth="1"/>
-    <col min="10" max="10" width="15.6640625" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="17.1640625" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="15.83203125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -815,213 +789,198 @@
       <c r="H1" s="1" t="s">
         <v>97</v>
       </c>
-      <c r="I1" s="2" t="s">
-        <v>101</v>
-      </c>
-      <c r="J1" s="1" t="s">
-        <v>102</v>
-      </c>
-      <c r="K1" s="1" t="s">
-        <v>103</v>
-      </c>
-      <c r="L1" s="1" t="s">
-        <v>104</v>
-      </c>
-    </row>
-    <row r="2" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A2" s="3" t="s">
+    </row>
+    <row r="2" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A2" s="2" t="s">
         <v>29</v>
       </c>
-      <c r="B2" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="C2" s="3" t="s">
+      <c r="B2" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="C2" s="2" t="s">
         <v>95</v>
       </c>
-      <c r="D2" s="3" t="s">
+      <c r="D2" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="E2" s="3">
+      <c r="E2" s="2">
         <v>2025</v>
       </c>
-      <c r="F2" s="7">
+      <c r="F2" s="5">
         <v>509983</v>
       </c>
-      <c r="G2" s="7">
+      <c r="G2" s="5">
         <v>508845</v>
       </c>
       <c r="H2" t="s">
         <v>98</v>
       </c>
-      <c r="I2" s="4"/>
-    </row>
-    <row r="3" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A3" s="3" t="s">
+    </row>
+    <row r="3" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A3" s="2" t="s">
         <v>59</v>
       </c>
-      <c r="B3" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="C3" s="3" t="s">
+      <c r="B3" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="C3" s="2" t="s">
         <v>95</v>
       </c>
-      <c r="D3" s="3" t="s">
+      <c r="D3" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="E3" s="3">
+      <c r="E3" s="2">
         <v>2025</v>
       </c>
-      <c r="F3" s="7">
+      <c r="F3" s="5">
         <v>95550</v>
       </c>
-      <c r="G3" s="7">
+      <c r="G3" s="5">
         <v>95378</v>
       </c>
       <c r="H3" t="s">
         <v>99</v>
       </c>
-      <c r="I3" s="4"/>
-    </row>
-    <row r="4" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A4" s="3" t="s">
-        <v>113</v>
-      </c>
-      <c r="B4" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="C4" s="3" t="s">
+    </row>
+    <row r="4" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A4" s="2" t="s">
+        <v>109</v>
+      </c>
+      <c r="B4" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="C4" s="2" t="s">
         <v>95</v>
       </c>
-      <c r="D4" s="3" t="s">
+      <c r="D4" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="E4" s="3">
+      <c r="E4" s="2">
         <v>2025</v>
       </c>
-      <c r="F4" s="7">
+      <c r="F4" s="5">
         <v>58745</v>
       </c>
-      <c r="G4" s="7">
+      <c r="G4" s="5">
         <v>58624</v>
       </c>
       <c r="H4" t="s">
         <v>100</v>
       </c>
-      <c r="I4" s="4"/>
-    </row>
-    <row r="5" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A5" s="3" t="s">
+    </row>
+    <row r="5" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A5" s="2" t="s">
         <v>29</v>
       </c>
-      <c r="B5" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="C5" s="3" t="s">
+      <c r="B5" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="C5" s="2" t="s">
         <v>96</v>
       </c>
-      <c r="D5" s="3" t="s">
+      <c r="D5" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="E5" s="3">
+      <c r="E5" s="2">
         <v>2025</v>
       </c>
-      <c r="F5" s="7">
+      <c r="F5" s="5">
         <v>1261465</v>
       </c>
-      <c r="G5" s="7">
+      <c r="G5" s="5">
         <v>1109790</v>
       </c>
       <c r="H5" t="s">
         <v>98</v>
       </c>
     </row>
-    <row r="6" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A6" s="3" t="s">
+    <row r="6" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A6" s="2" t="s">
         <v>59</v>
       </c>
-      <c r="B6" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="C6" s="3" t="s">
+      <c r="B6" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="C6" s="2" t="s">
         <v>96</v>
       </c>
-      <c r="D6" s="3" t="s">
+      <c r="D6" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="E6" s="3">
+      <c r="E6" s="2">
         <v>2025</v>
       </c>
-      <c r="F6" s="7">
+      <c r="F6" s="5">
         <v>622244</v>
       </c>
-      <c r="G6" s="7">
+      <c r="G6" s="5">
         <v>559308</v>
       </c>
       <c r="H6" t="s">
         <v>99</v>
       </c>
     </row>
-    <row r="7" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A7" s="3" t="s">
-        <v>113</v>
-      </c>
-      <c r="B7" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="C7" s="3" t="s">
+    <row r="7" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A7" s="2" t="s">
+        <v>109</v>
+      </c>
+      <c r="B7" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="C7" s="2" t="s">
         <v>96</v>
       </c>
-      <c r="D7" s="3" t="s">
+      <c r="D7" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="E7" s="3">
+      <c r="E7" s="2">
         <v>2025</v>
       </c>
-      <c r="F7" s="7">
+      <c r="F7" s="5">
         <v>436118</v>
       </c>
-      <c r="G7" s="7">
+      <c r="G7" s="5">
         <v>425641</v>
       </c>
       <c r="H7" t="s">
         <v>100</v>
       </c>
     </row>
-    <row r="8" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A8" s="3"/>
-    </row>
-    <row r="9" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A9" s="3"/>
-    </row>
-    <row r="10" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A10" s="3"/>
-    </row>
-    <row r="11" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A11" s="3"/>
-    </row>
-    <row r="12" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A12" s="3"/>
-    </row>
-    <row r="13" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A13" s="3"/>
-    </row>
-    <row r="14" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A14" s="3"/>
-    </row>
-    <row r="15" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A15" s="3"/>
-    </row>
-    <row r="16" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A16" s="3"/>
+    <row r="8" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A8" s="2"/>
+    </row>
+    <row r="9" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A9" s="2"/>
+    </row>
+    <row r="10" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A10" s="2"/>
+    </row>
+    <row r="11" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A11" s="2"/>
+    </row>
+    <row r="12" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A12" s="2"/>
+    </row>
+    <row r="13" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A13" s="2"/>
+    </row>
+    <row r="14" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A14" s="2"/>
+    </row>
+    <row r="15" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A15" s="2"/>
+    </row>
+    <row r="16" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A16" s="2"/>
     </row>
     <row r="17" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A17" s="3"/>
+      <c r="A17" s="2"/>
     </row>
     <row r="18" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A18" s="3"/>
+      <c r="A18" s="2"/>
     </row>
     <row r="19" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A19" s="3"/>
+      <c r="A19" s="2"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -1053,747 +1012,747 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A1" s="8" t="s">
+      <c r="A1" s="6" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="8" t="s">
+      <c r="B1" s="6" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="8" t="s">
+      <c r="C1" s="6" t="s">
         <v>14</v>
       </c>
-      <c r="D1" s="8" t="s">
+      <c r="D1" s="6" t="s">
         <v>15</v>
       </c>
-      <c r="E1" s="8" t="s">
+      <c r="E1" s="6" t="s">
         <v>97</v>
       </c>
-      <c r="F1" s="5" t="s">
+      <c r="F1" s="3" t="s">
         <v>16</v>
       </c>
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A2" s="6" t="s">
+      <c r="A2" s="4" t="s">
+        <v>101</v>
+      </c>
+      <c r="B2" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="C2" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="E2" s="7"/>
+      <c r="F2" s="3" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A3" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="B3" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="E3" s="7"/>
+      <c r="F3" s="3" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A4" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="B4" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="E4" s="7"/>
+    </row>
+    <row r="5" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A5" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="B5" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="E5" s="7"/>
+    </row>
+    <row r="6" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A6" s="4" t="s">
+        <v>102</v>
+      </c>
+      <c r="B6" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="C6" s="4" t="s">
+        <v>23</v>
+      </c>
+      <c r="E6" s="7"/>
+    </row>
+    <row r="7" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A7" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="B7" s="4" t="s">
+        <v>25</v>
+      </c>
+      <c r="E7" s="7"/>
+    </row>
+    <row r="8" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A8" s="4" t="s">
+        <v>26</v>
+      </c>
+      <c r="B8" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="E8" s="7"/>
+    </row>
+    <row r="9" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A9" s="4" t="s">
+        <v>27</v>
+      </c>
+      <c r="B9" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="E9" s="7"/>
+    </row>
+    <row r="10" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A10" s="4" t="s">
+        <v>28</v>
+      </c>
+      <c r="B10" s="4" t="s">
+        <v>25</v>
+      </c>
+      <c r="E10" s="7"/>
+    </row>
+    <row r="11" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A11" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="B11" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="E11" s="7"/>
+    </row>
+    <row r="12" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A12" s="4" t="s">
+        <v>29</v>
+      </c>
+      <c r="B12" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="E12" s="7"/>
+    </row>
+    <row r="13" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A13" s="4" t="s">
+        <v>103</v>
+      </c>
+      <c r="B13" s="4" t="s">
+        <v>25</v>
+      </c>
+      <c r="C13" s="4" t="s">
+        <v>30</v>
+      </c>
+      <c r="E13" s="7"/>
+    </row>
+    <row r="14" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A14" s="4" t="s">
+        <v>31</v>
+      </c>
+      <c r="B14" s="4" t="s">
+        <v>32</v>
+      </c>
+      <c r="E14" s="7"/>
+    </row>
+    <row r="15" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A15" s="4" t="s">
+        <v>33</v>
+      </c>
+      <c r="B15" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="E15" s="7"/>
+    </row>
+    <row r="16" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A16" s="4" t="s">
+        <v>34</v>
+      </c>
+      <c r="B16" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="E16" s="7"/>
+    </row>
+    <row r="17" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A17" s="4" t="s">
+        <v>35</v>
+      </c>
+      <c r="B17" s="4" t="s">
+        <v>36</v>
+      </c>
+      <c r="E17" s="7"/>
+    </row>
+    <row r="18" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A18" s="4" t="s">
+        <v>37</v>
+      </c>
+      <c r="B18" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="E18" s="7"/>
+    </row>
+    <row r="19" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A19" s="4" t="s">
+        <v>38</v>
+      </c>
+      <c r="B19" s="4" t="s">
+        <v>32</v>
+      </c>
+      <c r="E19" s="7"/>
+    </row>
+    <row r="20" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A20" s="4" t="s">
+        <v>109</v>
+      </c>
+      <c r="B20" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="E20" s="7"/>
+    </row>
+    <row r="21" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A21" s="4" t="s">
+        <v>39</v>
+      </c>
+      <c r="B21" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="E21" s="7"/>
+    </row>
+    <row r="22" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A22" s="4" t="s">
+        <v>40</v>
+      </c>
+      <c r="B22" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="E22" s="7"/>
+    </row>
+    <row r="23" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A23" s="4" t="s">
+        <v>104</v>
+      </c>
+      <c r="B23" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="C23" s="4" t="s">
+        <v>41</v>
+      </c>
+      <c r="E23" s="7"/>
+    </row>
+    <row r="24" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A24" s="4" t="s">
+        <v>42</v>
+      </c>
+      <c r="B24" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="E24" s="7"/>
+    </row>
+    <row r="25" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A25" s="4" t="s">
+        <v>43</v>
+      </c>
+      <c r="B25" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="E25" s="7"/>
+    </row>
+    <row r="26" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A26" s="4" t="s">
+        <v>44</v>
+      </c>
+      <c r="B26" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="E26" s="7"/>
+    </row>
+    <row r="27" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A27" s="4" t="s">
+        <v>45</v>
+      </c>
+      <c r="B27" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="E27" s="7"/>
+    </row>
+    <row r="28" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A28" s="4" t="s">
+        <v>46</v>
+      </c>
+      <c r="B28" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="E28" s="7"/>
+    </row>
+    <row r="29" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A29" s="4" t="s">
+        <v>47</v>
+      </c>
+      <c r="B29" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="E29" s="7"/>
+    </row>
+    <row r="30" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A30" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="B30" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="E30" s="7"/>
+    </row>
+    <row r="31" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A31" s="4" t="s">
+        <v>48</v>
+      </c>
+      <c r="B31" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="E31" s="7"/>
+    </row>
+    <row r="32" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A32" s="4" t="s">
+        <v>49</v>
+      </c>
+      <c r="B32" s="4" t="s">
+        <v>32</v>
+      </c>
+      <c r="E32" s="7"/>
+    </row>
+    <row r="33" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A33" s="4" t="s">
+        <v>50</v>
+      </c>
+      <c r="B33" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="E33" s="7"/>
+    </row>
+    <row r="34" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A34" s="4" t="s">
+        <v>51</v>
+      </c>
+      <c r="B34" s="4" t="s">
+        <v>32</v>
+      </c>
+      <c r="E34" s="7"/>
+    </row>
+    <row r="35" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A35" s="4" t="s">
         <v>105</v>
       </c>
-      <c r="B2" s="6" t="s">
-        <v>13</v>
-      </c>
-      <c r="C2" s="6" t="s">
-        <v>17</v>
-      </c>
-      <c r="E2" s="9"/>
-      <c r="F2" s="5" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A3" s="6" t="s">
-        <v>19</v>
-      </c>
-      <c r="B3" s="6" t="s">
-        <v>11</v>
-      </c>
-      <c r="E3" s="9"/>
-      <c r="F3" s="5" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A4" s="6" t="s">
-        <v>21</v>
-      </c>
-      <c r="B4" s="6" t="s">
-        <v>13</v>
-      </c>
-      <c r="E4" s="9"/>
-    </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A5" s="6" t="s">
-        <v>22</v>
-      </c>
-      <c r="B5" s="6" t="s">
-        <v>11</v>
-      </c>
-      <c r="E5" s="9"/>
-    </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A6" s="6" t="s">
+      <c r="B35" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="C35" s="4" t="s">
+        <v>52</v>
+      </c>
+      <c r="E35" s="7"/>
+    </row>
+    <row r="36" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A36" s="4" t="s">
+        <v>53</v>
+      </c>
+      <c r="B36" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="E36" s="7"/>
+    </row>
+    <row r="37" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A37" s="4" t="s">
+        <v>54</v>
+      </c>
+      <c r="B37" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="E37" s="7"/>
+    </row>
+    <row r="38" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A38" s="4" t="s">
+        <v>55</v>
+      </c>
+      <c r="B38" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="E38" s="7"/>
+    </row>
+    <row r="39" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A39" s="4" t="s">
+        <v>56</v>
+      </c>
+      <c r="B39" s="4" t="s">
+        <v>32</v>
+      </c>
+      <c r="E39" s="7"/>
+    </row>
+    <row r="40" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A40" s="4" t="s">
         <v>106</v>
       </c>
-      <c r="B6" s="6" t="s">
-        <v>11</v>
-      </c>
-      <c r="C6" s="6" t="s">
-        <v>23</v>
-      </c>
-      <c r="E6" s="9"/>
-    </row>
-    <row r="7" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A7" s="6" t="s">
-        <v>24</v>
-      </c>
-      <c r="B7" s="6" t="s">
+      <c r="B40" s="4" t="s">
+        <v>32</v>
+      </c>
+      <c r="C40" s="4" t="s">
+        <v>57</v>
+      </c>
+      <c r="E40" s="7"/>
+    </row>
+    <row r="41" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A41" s="4" t="s">
+        <v>58</v>
+      </c>
+      <c r="B41" s="4" t="s">
+        <v>32</v>
+      </c>
+      <c r="E41" s="7"/>
+    </row>
+    <row r="42" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A42" s="4" t="s">
+        <v>59</v>
+      </c>
+      <c r="B42" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="E42" s="7"/>
+    </row>
+    <row r="43" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A43" s="4" t="s">
+        <v>60</v>
+      </c>
+      <c r="B43" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="E43" s="7"/>
+    </row>
+    <row r="44" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A44" s="4" t="s">
+        <v>61</v>
+      </c>
+      <c r="B44" s="4" t="s">
+        <v>36</v>
+      </c>
+      <c r="E44" s="7"/>
+    </row>
+    <row r="45" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A45" s="4" t="s">
+        <v>62</v>
+      </c>
+      <c r="B45" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="E45" s="7"/>
+    </row>
+    <row r="46" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A46" s="4" t="s">
+        <v>63</v>
+      </c>
+      <c r="B46" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="E46" s="7"/>
+    </row>
+    <row r="47" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A47" s="4" t="s">
+        <v>64</v>
+      </c>
+      <c r="B47" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="E47" s="7"/>
+    </row>
+    <row r="48" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A48" s="4" t="s">
+        <v>65</v>
+      </c>
+      <c r="B48" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="E48" s="7"/>
+    </row>
+    <row r="49" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A49" s="4" t="s">
+        <v>66</v>
+      </c>
+      <c r="B49" s="4" t="s">
+        <v>32</v>
+      </c>
+      <c r="E49" s="7"/>
+    </row>
+    <row r="50" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A50" s="4" t="s">
+        <v>107</v>
+      </c>
+      <c r="B50" s="4" t="s">
         <v>25</v>
       </c>
-      <c r="E7" s="9"/>
-    </row>
-    <row r="8" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A8" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="B8" s="6" t="s">
-        <v>13</v>
-      </c>
-      <c r="E8" s="9"/>
-    </row>
-    <row r="9" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A9" s="6" t="s">
-        <v>27</v>
-      </c>
-      <c r="B9" s="6" t="s">
-        <v>11</v>
-      </c>
-      <c r="E9" s="9"/>
-    </row>
-    <row r="10" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A10" s="6" t="s">
-        <v>28</v>
-      </c>
-      <c r="B10" s="6" t="s">
+      <c r="C50" s="4" t="s">
+        <v>67</v>
+      </c>
+      <c r="E50" s="7"/>
+    </row>
+    <row r="51" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A51" s="4" t="s">
+        <v>68</v>
+      </c>
+      <c r="B51" s="4" t="s">
+        <v>36</v>
+      </c>
+      <c r="E51" s="7"/>
+    </row>
+    <row r="52" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A52" s="4" t="s">
+        <v>69</v>
+      </c>
+      <c r="B52" s="4" t="s">
+        <v>32</v>
+      </c>
+      <c r="E52" s="7"/>
+    </row>
+    <row r="53" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A53" s="4" t="s">
+        <v>70</v>
+      </c>
+      <c r="B53" s="4" t="s">
+        <v>36</v>
+      </c>
+      <c r="E53" s="7"/>
+    </row>
+    <row r="54" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A54" s="4" t="s">
+        <v>71</v>
+      </c>
+      <c r="B54" s="4" t="s">
         <v>25</v>
       </c>
-      <c r="E10" s="9"/>
-    </row>
-    <row r="11" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A11" s="6" t="s">
-        <v>7</v>
-      </c>
-      <c r="B11" s="6" t="s">
-        <v>8</v>
-      </c>
-      <c r="E11" s="9"/>
-    </row>
-    <row r="12" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A12" s="6" t="s">
-        <v>29</v>
-      </c>
-      <c r="B12" s="6" t="s">
-        <v>8</v>
-      </c>
-      <c r="E12" s="9"/>
-    </row>
-    <row r="13" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A13" s="6" t="s">
-        <v>107</v>
-      </c>
-      <c r="B13" s="6" t="s">
+      <c r="E54" s="7"/>
+    </row>
+    <row r="55" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A55" s="4" t="s">
+        <v>72</v>
+      </c>
+      <c r="B55" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="E55" s="7"/>
+    </row>
+    <row r="56" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A56" s="4" t="s">
+        <v>73</v>
+      </c>
+      <c r="B56" s="4" t="s">
         <v>25</v>
       </c>
-      <c r="C13" s="6" t="s">
-        <v>30</v>
-      </c>
-      <c r="E13" s="9"/>
-    </row>
-    <row r="14" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A14" s="6" t="s">
-        <v>31</v>
-      </c>
-      <c r="B14" s="6" t="s">
+      <c r="E56" s="7"/>
+    </row>
+    <row r="57" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A57" s="4" t="s">
+        <v>74</v>
+      </c>
+      <c r="B57" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="E57" s="7"/>
+    </row>
+    <row r="58" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A58" s="4" t="s">
+        <v>75</v>
+      </c>
+      <c r="B58" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="E58" s="7"/>
+    </row>
+    <row r="59" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A59" s="4" t="s">
+        <v>76</v>
+      </c>
+      <c r="B59" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="E59" s="7"/>
+    </row>
+    <row r="60" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A60" s="4" t="s">
+        <v>77</v>
+      </c>
+      <c r="B60" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="E60" s="7"/>
+    </row>
+    <row r="61" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A61" s="4" t="s">
+        <v>78</v>
+      </c>
+      <c r="B61" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="E61" s="7"/>
+    </row>
+    <row r="62" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A62" s="4" t="s">
+        <v>79</v>
+      </c>
+      <c r="B62" s="4" t="s">
         <v>32</v>
       </c>
-      <c r="E14" s="9"/>
-    </row>
-    <row r="15" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A15" s="6" t="s">
-        <v>33</v>
-      </c>
-      <c r="B15" s="6" t="s">
-        <v>11</v>
-      </c>
-      <c r="E15" s="9"/>
-    </row>
-    <row r="16" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A16" s="6" t="s">
-        <v>34</v>
-      </c>
-      <c r="B16" s="6" t="s">
-        <v>8</v>
-      </c>
-      <c r="E16" s="9"/>
-    </row>
-    <row r="17" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A17" s="6" t="s">
-        <v>35</v>
-      </c>
-      <c r="B17" s="6" t="s">
-        <v>36</v>
-      </c>
-      <c r="E17" s="9"/>
-    </row>
-    <row r="18" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A18" s="6" t="s">
-        <v>37</v>
-      </c>
-      <c r="B18" s="6" t="s">
-        <v>11</v>
-      </c>
-      <c r="E18" s="9"/>
-    </row>
-    <row r="19" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A19" s="6" t="s">
-        <v>38</v>
-      </c>
-      <c r="B19" s="6" t="s">
+      <c r="E62" s="7"/>
+    </row>
+    <row r="63" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A63" s="4" t="s">
+        <v>80</v>
+      </c>
+      <c r="B63" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="E63" s="7"/>
+    </row>
+    <row r="64" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A64" s="4" t="s">
+        <v>108</v>
+      </c>
+      <c r="B64" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="C64" s="4" t="s">
+        <v>81</v>
+      </c>
+      <c r="E64" s="7"/>
+    </row>
+    <row r="65" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A65" s="4" t="s">
+        <v>82</v>
+      </c>
+      <c r="B65" s="4" t="s">
         <v>32</v>
       </c>
-      <c r="E19" s="9"/>
-    </row>
-    <row r="20" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A20" s="6" t="s">
-        <v>113</v>
-      </c>
-      <c r="B20" s="6" t="s">
-        <v>8</v>
-      </c>
-      <c r="E20" s="9"/>
-    </row>
-    <row r="21" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A21" s="6" t="s">
-        <v>39</v>
-      </c>
-      <c r="B21" s="6" t="s">
-        <v>8</v>
-      </c>
-      <c r="E21" s="9"/>
-    </row>
-    <row r="22" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A22" s="6" t="s">
-        <v>40</v>
-      </c>
-      <c r="B22" s="6" t="s">
-        <v>11</v>
-      </c>
-      <c r="E22" s="9"/>
-    </row>
-    <row r="23" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A23" s="6" t="s">
-        <v>108</v>
-      </c>
-      <c r="B23" s="6" t="s">
-        <v>13</v>
-      </c>
-      <c r="C23" s="6" t="s">
-        <v>41</v>
-      </c>
-      <c r="E23" s="9"/>
-    </row>
-    <row r="24" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A24" s="6" t="s">
-        <v>42</v>
-      </c>
-      <c r="B24" s="6" t="s">
-        <v>8</v>
-      </c>
-      <c r="E24" s="9"/>
-    </row>
-    <row r="25" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A25" s="6" t="s">
-        <v>43</v>
-      </c>
-      <c r="B25" s="6" t="s">
-        <v>11</v>
-      </c>
-      <c r="E25" s="9"/>
-    </row>
-    <row r="26" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A26" s="6" t="s">
-        <v>44</v>
-      </c>
-      <c r="B26" s="6" t="s">
-        <v>11</v>
-      </c>
-      <c r="E26" s="9"/>
-    </row>
-    <row r="27" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A27" s="6" t="s">
-        <v>45</v>
-      </c>
-      <c r="B27" s="6" t="s">
-        <v>13</v>
-      </c>
-      <c r="E27" s="9"/>
-    </row>
-    <row r="28" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A28" s="6" t="s">
-        <v>46</v>
-      </c>
-      <c r="B28" s="6" t="s">
-        <v>13</v>
-      </c>
-      <c r="E28" s="9"/>
-    </row>
-    <row r="29" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A29" s="6" t="s">
-        <v>47</v>
-      </c>
-      <c r="B29" s="6" t="s">
-        <v>11</v>
-      </c>
-      <c r="E29" s="9"/>
-    </row>
-    <row r="30" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A30" s="6" t="s">
-        <v>10</v>
-      </c>
-      <c r="B30" s="6" t="s">
-        <v>11</v>
-      </c>
-      <c r="E30" s="9"/>
-    </row>
-    <row r="31" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A31" s="6" t="s">
-        <v>48</v>
-      </c>
-      <c r="B31" s="6" t="s">
-        <v>13</v>
-      </c>
-      <c r="E31" s="9"/>
-    </row>
-    <row r="32" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A32" s="6" t="s">
-        <v>49</v>
-      </c>
-      <c r="B32" s="6" t="s">
+      <c r="E65" s="7"/>
+    </row>
+    <row r="66" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A66" s="4" t="s">
+        <v>83</v>
+      </c>
+      <c r="B66" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="E66" s="7"/>
+    </row>
+    <row r="67" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A67" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="B67" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="E67" s="7"/>
+    </row>
+    <row r="68" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A68" s="4" t="s">
+        <v>84</v>
+      </c>
+      <c r="B68" s="4" t="s">
         <v>32</v>
       </c>
-      <c r="E32" s="9"/>
-    </row>
-    <row r="33" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A33" s="6" t="s">
-        <v>50</v>
-      </c>
-      <c r="B33" s="6" t="s">
-        <v>8</v>
-      </c>
-      <c r="E33" s="9"/>
-    </row>
-    <row r="34" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A34" s="6" t="s">
-        <v>51</v>
-      </c>
-      <c r="B34" s="6" t="s">
+      <c r="E68" s="7"/>
+    </row>
+    <row r="69" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A69" s="4" t="s">
+        <v>85</v>
+      </c>
+      <c r="B69" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="E69" s="7"/>
+    </row>
+    <row r="70" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A70" s="4" t="s">
+        <v>86</v>
+      </c>
+      <c r="B70" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="E70" s="7"/>
+    </row>
+    <row r="71" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A71" s="4" t="s">
+        <v>87</v>
+      </c>
+      <c r="B71" s="4" t="s">
         <v>32</v>
       </c>
-      <c r="E34" s="9"/>
-    </row>
-    <row r="35" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A35" s="6" t="s">
-        <v>109</v>
-      </c>
-      <c r="B35" s="6" t="s">
-        <v>11</v>
-      </c>
-      <c r="C35" s="6" t="s">
-        <v>52</v>
-      </c>
-      <c r="E35" s="9"/>
-    </row>
-    <row r="36" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A36" s="6" t="s">
-        <v>53</v>
-      </c>
-      <c r="B36" s="6" t="s">
-        <v>11</v>
-      </c>
-      <c r="E36" s="9"/>
-    </row>
-    <row r="37" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A37" s="6" t="s">
-        <v>54</v>
-      </c>
-      <c r="B37" s="6" t="s">
-        <v>13</v>
-      </c>
-      <c r="E37" s="9"/>
-    </row>
-    <row r="38" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A38" s="6" t="s">
-        <v>55</v>
-      </c>
-      <c r="B38" s="6" t="s">
-        <v>13</v>
-      </c>
-      <c r="E38" s="9"/>
-    </row>
-    <row r="39" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A39" s="6" t="s">
-        <v>56</v>
-      </c>
-      <c r="B39" s="6" t="s">
+      <c r="E71" s="7"/>
+    </row>
+    <row r="72" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A72" s="4" t="s">
+        <v>88</v>
+      </c>
+      <c r="B72" s="4" t="s">
+        <v>25</v>
+      </c>
+      <c r="E72" s="7"/>
+    </row>
+    <row r="73" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A73" s="4" t="s">
+        <v>89</v>
+      </c>
+      <c r="B73" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="E73" s="7"/>
+    </row>
+    <row r="74" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A74" s="4" t="s">
+        <v>90</v>
+      </c>
+      <c r="B74" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="E74" s="7"/>
+    </row>
+    <row r="75" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A75" s="4" t="s">
+        <v>91</v>
+      </c>
+      <c r="B75" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="E75" s="7"/>
+    </row>
+    <row r="76" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A76" s="4" t="s">
+        <v>92</v>
+      </c>
+      <c r="B76" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="E76" s="7"/>
+    </row>
+    <row r="77" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A77" s="4" t="s">
+        <v>93</v>
+      </c>
+      <c r="B77" s="4" t="s">
         <v>32</v>
       </c>
-      <c r="E39" s="9"/>
-    </row>
-    <row r="40" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A40" s="6" t="s">
-        <v>110</v>
-      </c>
-      <c r="B40" s="6" t="s">
-        <v>32</v>
-      </c>
-      <c r="C40" s="6" t="s">
-        <v>57</v>
-      </c>
-      <c r="E40" s="9"/>
-    </row>
-    <row r="41" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A41" s="6" t="s">
-        <v>58</v>
-      </c>
-      <c r="B41" s="6" t="s">
-        <v>32</v>
-      </c>
-      <c r="E41" s="9"/>
-    </row>
-    <row r="42" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A42" s="6" t="s">
-        <v>59</v>
-      </c>
-      <c r="B42" s="6" t="s">
-        <v>8</v>
-      </c>
-      <c r="E42" s="9"/>
-    </row>
-    <row r="43" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A43" s="6" t="s">
-        <v>60</v>
-      </c>
-      <c r="B43" s="6" t="s">
-        <v>13</v>
-      </c>
-      <c r="E43" s="9"/>
-    </row>
-    <row r="44" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A44" s="6" t="s">
-        <v>61</v>
-      </c>
-      <c r="B44" s="6" t="s">
-        <v>36</v>
-      </c>
-      <c r="E44" s="9"/>
-    </row>
-    <row r="45" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A45" s="6" t="s">
-        <v>62</v>
-      </c>
-      <c r="B45" s="6" t="s">
-        <v>13</v>
-      </c>
-      <c r="E45" s="9"/>
-    </row>
-    <row r="46" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A46" s="6" t="s">
-        <v>63</v>
-      </c>
-      <c r="B46" s="6" t="s">
-        <v>8</v>
-      </c>
-      <c r="E46" s="9"/>
-    </row>
-    <row r="47" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A47" s="6" t="s">
-        <v>64</v>
-      </c>
-      <c r="B47" s="6" t="s">
-        <v>13</v>
-      </c>
-      <c r="E47" s="9"/>
-    </row>
-    <row r="48" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A48" s="6" t="s">
-        <v>65</v>
-      </c>
-      <c r="B48" s="6" t="s">
-        <v>8</v>
-      </c>
-      <c r="E48" s="9"/>
-    </row>
-    <row r="49" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A49" s="6" t="s">
-        <v>66</v>
-      </c>
-      <c r="B49" s="6" t="s">
-        <v>32</v>
-      </c>
-      <c r="E49" s="9"/>
-    </row>
-    <row r="50" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A50" s="6" t="s">
-        <v>111</v>
-      </c>
-      <c r="B50" s="6" t="s">
-        <v>25</v>
-      </c>
-      <c r="C50" s="6" t="s">
-        <v>67</v>
-      </c>
-      <c r="E50" s="9"/>
-    </row>
-    <row r="51" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A51" s="6" t="s">
-        <v>68</v>
-      </c>
-      <c r="B51" s="6" t="s">
-        <v>36</v>
-      </c>
-      <c r="E51" s="9"/>
-    </row>
-    <row r="52" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A52" s="6" t="s">
-        <v>69</v>
-      </c>
-      <c r="B52" s="6" t="s">
-        <v>32</v>
-      </c>
-      <c r="E52" s="9"/>
-    </row>
-    <row r="53" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A53" s="6" t="s">
-        <v>70</v>
-      </c>
-      <c r="B53" s="6" t="s">
-        <v>36</v>
-      </c>
-      <c r="E53" s="9"/>
-    </row>
-    <row r="54" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A54" s="6" t="s">
-        <v>71</v>
-      </c>
-      <c r="B54" s="6" t="s">
-        <v>25</v>
-      </c>
-      <c r="E54" s="9"/>
-    </row>
-    <row r="55" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A55" s="6" t="s">
-        <v>72</v>
-      </c>
-      <c r="B55" s="6" t="s">
-        <v>11</v>
-      </c>
-      <c r="E55" s="9"/>
-    </row>
-    <row r="56" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A56" s="6" t="s">
-        <v>73</v>
-      </c>
-      <c r="B56" s="6" t="s">
-        <v>25</v>
-      </c>
-      <c r="E56" s="9"/>
-    </row>
-    <row r="57" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A57" s="6" t="s">
-        <v>74</v>
-      </c>
-      <c r="B57" s="6" t="s">
-        <v>11</v>
-      </c>
-      <c r="E57" s="9"/>
-    </row>
-    <row r="58" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A58" s="6" t="s">
-        <v>75</v>
-      </c>
-      <c r="B58" s="6" t="s">
-        <v>13</v>
-      </c>
-      <c r="E58" s="9"/>
-    </row>
-    <row r="59" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A59" s="6" t="s">
-        <v>76</v>
-      </c>
-      <c r="B59" s="6" t="s">
-        <v>13</v>
-      </c>
-      <c r="E59" s="9"/>
-    </row>
-    <row r="60" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A60" s="6" t="s">
-        <v>77</v>
-      </c>
-      <c r="B60" s="6" t="s">
-        <v>13</v>
-      </c>
-      <c r="E60" s="9"/>
-    </row>
-    <row r="61" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A61" s="6" t="s">
-        <v>78</v>
-      </c>
-      <c r="B61" s="6" t="s">
-        <v>13</v>
-      </c>
-      <c r="E61" s="9"/>
-    </row>
-    <row r="62" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A62" s="6" t="s">
-        <v>79</v>
-      </c>
-      <c r="B62" s="6" t="s">
-        <v>32</v>
-      </c>
-      <c r="E62" s="9"/>
-    </row>
-    <row r="63" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A63" s="6" t="s">
-        <v>80</v>
-      </c>
-      <c r="B63" s="6" t="s">
-        <v>13</v>
-      </c>
-      <c r="E63" s="9"/>
-    </row>
-    <row r="64" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A64" s="6" t="s">
-        <v>112</v>
-      </c>
-      <c r="B64" s="6" t="s">
-        <v>11</v>
-      </c>
-      <c r="C64" s="6" t="s">
-        <v>81</v>
-      </c>
-      <c r="E64" s="9"/>
-    </row>
-    <row r="65" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A65" s="6" t="s">
-        <v>82</v>
-      </c>
-      <c r="B65" s="6" t="s">
-        <v>32</v>
-      </c>
-      <c r="E65" s="9"/>
-    </row>
-    <row r="66" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A66" s="6" t="s">
-        <v>83</v>
-      </c>
-      <c r="B66" s="6" t="s">
-        <v>8</v>
-      </c>
-      <c r="E66" s="9"/>
-    </row>
-    <row r="67" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A67" s="6" t="s">
-        <v>12</v>
-      </c>
-      <c r="B67" s="6" t="s">
-        <v>13</v>
-      </c>
-      <c r="E67" s="9"/>
-    </row>
-    <row r="68" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A68" s="6" t="s">
-        <v>84</v>
-      </c>
-      <c r="B68" s="6" t="s">
-        <v>32</v>
-      </c>
-      <c r="E68" s="9"/>
-    </row>
-    <row r="69" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A69" s="6" t="s">
-        <v>85</v>
-      </c>
-      <c r="B69" s="6" t="s">
-        <v>11</v>
-      </c>
-      <c r="E69" s="9"/>
-    </row>
-    <row r="70" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A70" s="6" t="s">
-        <v>86</v>
-      </c>
-      <c r="B70" s="6" t="s">
-        <v>8</v>
-      </c>
-      <c r="E70" s="9"/>
-    </row>
-    <row r="71" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A71" s="6" t="s">
-        <v>87</v>
-      </c>
-      <c r="B71" s="6" t="s">
-        <v>32</v>
-      </c>
-      <c r="E71" s="9"/>
-    </row>
-    <row r="72" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A72" s="6" t="s">
-        <v>88</v>
-      </c>
-      <c r="B72" s="6" t="s">
-        <v>25</v>
-      </c>
-      <c r="E72" s="9"/>
-    </row>
-    <row r="73" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A73" s="6" t="s">
-        <v>89</v>
-      </c>
-      <c r="B73" s="6" t="s">
-        <v>11</v>
-      </c>
-      <c r="E73" s="9"/>
-    </row>
-    <row r="74" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A74" s="6" t="s">
-        <v>90</v>
-      </c>
-      <c r="B74" s="6" t="s">
-        <v>11</v>
-      </c>
-      <c r="E74" s="9"/>
-    </row>
-    <row r="75" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A75" s="6" t="s">
-        <v>91</v>
-      </c>
-      <c r="B75" s="6" t="s">
-        <v>13</v>
-      </c>
-      <c r="E75" s="9"/>
-    </row>
-    <row r="76" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A76" s="6" t="s">
-        <v>92</v>
-      </c>
-      <c r="B76" s="6" t="s">
-        <v>8</v>
-      </c>
-      <c r="E76" s="9"/>
-    </row>
-    <row r="77" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A77" s="6" t="s">
-        <v>93</v>
-      </c>
-      <c r="B77" s="6" t="s">
-        <v>32</v>
-      </c>
-      <c r="E77" s="9"/>
+      <c r="E77" s="7"/>
     </row>
     <row r="78" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A78" s="6" t="s">
+      <c r="A78" s="4" t="s">
         <v>94</v>
       </c>
-      <c r="B78" s="6" t="s">
-        <v>11</v>
-      </c>
-      <c r="E78" s="9"/>
+      <c r="B78" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="E78" s="7"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
